--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -677,10 +677,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -703,8 +703,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -734,6 +749,43 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -742,9 +794,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -759,14 +833,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -774,74 +841,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -856,7 +856,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +892,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,19 +922,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -904,67 +1024,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -976,67 +1036,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1054,7 +1054,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1083,6 +1083,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1094,6 +1103,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1113,15 +1133,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1136,17 +1147,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1155,145 +1155,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -2284,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
@@ -3993,7 +3993,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4298,7 +4298,7 @@
         <v>40</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -4309,7 +4309,7 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -4320,7 +4320,7 @@
         <v>40</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -4342,7 +4342,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>10</v>
@@ -4353,7 +4353,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35">
         <v>12</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36">
         <v>14</v>
@@ -4392,12 +4392,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1" spans="1:3">
+    <row r="37" spans="1:3">
       <c r="A37">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -4405,10 +4405,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -4416,10 +4416,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C39">
         <v>10</v>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C40">
         <v>10</v>
@@ -4438,18 +4438,18 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
+        <v>42</v>
+      </c>
+      <c r="B41">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1" spans="1:3">
+      <c r="A42">
         <v>50</v>
-      </c>
-      <c r="B41">
-        <v>11</v>
-      </c>
-      <c r="C41">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42">
-        <v>51</v>
       </c>
       <c r="B42">
         <v>3</v>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44">
         <v>6</v>
@@ -4482,7 +4482,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45">
         <v>8</v>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>11</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48">
         <v>4</v>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>6</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50">
         <v>8</v>
@@ -4548,7 +4548,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51">
         <v>11</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52">
         <v>3</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53">
         <v>4</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -4592,7 +4592,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55">
         <v>8</v>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B56">
         <v>11</v>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>10</v>
@@ -4625,10 +4625,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B58">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>10</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B59">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C59">
         <v>10</v>
@@ -4647,10 +4647,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C60">
         <v>10</v>
@@ -4658,21 +4658,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B61">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C62">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C63">
         <v>10</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B64">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C64">
         <v>10</v>
@@ -4702,10 +4702,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C65">
         <v>10</v>
@@ -4713,10 +4713,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C66">
         <v>10</v>
@@ -4724,10 +4724,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C67">
         <v>10</v>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B68">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C68">
         <v>10</v>
@@ -4746,10 +4746,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69">
         <v>10</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B70">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C70">
         <v>10</v>
@@ -4771,7 +4771,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>10</v>
@@ -4782,7 +4782,7 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C72">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C73">
         <v>10</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -4812,10 +4812,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B75">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C75">
         <v>10</v>
@@ -4823,10 +4823,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C76">
         <v>10</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B77">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -4848,7 +4848,7 @@
         <v>71</v>
       </c>
       <c r="B78">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>10</v>
@@ -4859,7 +4859,7 @@
         <v>71</v>
       </c>
       <c r="B79">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>10</v>
@@ -4867,10 +4867,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C80">
         <v>10</v>
@@ -4878,10 +4878,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B81">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C81">
         <v>10</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B82">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C82">
         <v>10</v>
@@ -4900,10 +4900,10 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B83">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C83">
         <v>10</v>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B84">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84">
         <v>10</v>
@@ -4925,7 +4925,7 @@
         <v>72</v>
       </c>
       <c r="B85">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C85">
         <v>10</v>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -4944,10 +4944,10 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B87">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C87">
         <v>10</v>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B88">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C88">
         <v>10</v>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B89">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C89">
         <v>10</v>
@@ -4977,10 +4977,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B90">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C90">
         <v>10</v>
@@ -4991,7 +4991,7 @@
         <v>73</v>
       </c>
       <c r="B91">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C91">
         <v>10</v>
@@ -5002,7 +5002,7 @@
         <v>73</v>
       </c>
       <c r="B92">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -5010,65 +5010,65 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C94">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B95">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C95">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B96">
         <v>11</v>
       </c>
       <c r="C96">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>1020</v>
+        <v>73</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98">
         <v>15</v>
@@ -5076,10 +5076,10 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>15</v>
@@ -5087,10 +5087,10 @@
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C100">
         <v>15</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B101">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C101">
         <v>15</v>
@@ -5109,10 +5109,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
         <v>15</v>
@@ -5120,10 +5120,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B103">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C103">
         <v>15</v>
@@ -5131,10 +5131,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B104">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C104">
         <v>15</v>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C105">
         <v>15</v>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="B106">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C106">
         <v>15</v>
@@ -5164,10 +5164,10 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B107">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>15</v>
@@ -5175,10 +5175,10 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B108">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C108">
         <v>15</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B109">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C109">
         <v>15</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C110">
         <v>15</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B111">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C111">
         <v>15</v>
@@ -5219,10 +5219,10 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B112">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -5230,57 +5230,57 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C113">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C114">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B115">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C115">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B116">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B117">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C117">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -5288,7 +5288,7 @@
         <v>2010</v>
       </c>
       <c r="B118">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C118">
         <v>10</v>
@@ -5299,7 +5299,7 @@
         <v>2010</v>
       </c>
       <c r="B119">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C119">
         <v>10</v>
@@ -5310,7 +5310,7 @@
         <v>2010</v>
       </c>
       <c r="B120">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C120">
         <v>10</v>
@@ -5318,10 +5318,10 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C121">
         <v>10</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -5340,10 +5340,10 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C123">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B124">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C124">
         <v>10</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -5376,7 +5376,7 @@
         <v>2020</v>
       </c>
       <c r="B126">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -5387,7 +5387,7 @@
         <v>2020</v>
       </c>
       <c r="B127">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C127">
         <v>10</v>
@@ -5398,7 +5398,7 @@
         <v>2020</v>
       </c>
       <c r="B128">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C128">
         <v>10</v>
@@ -5409,7 +5409,7 @@
         <v>2020</v>
       </c>
       <c r="B129">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C129">
         <v>10</v>
@@ -5420,7 +5420,7 @@
         <v>2020</v>
       </c>
       <c r="B130">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C130">
         <v>10</v>
@@ -5431,7 +5431,7 @@
         <v>2020</v>
       </c>
       <c r="B131">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C131">
         <v>10</v>
@@ -5442,7 +5442,7 @@
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C132">
         <v>10</v>
@@ -5453,7 +5453,7 @@
         <v>2020</v>
       </c>
       <c r="B133">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C133">
         <v>10</v>
@@ -5464,9 +5464,64 @@
         <v>2020</v>
       </c>
       <c r="B134">
+        <v>9</v>
+      </c>
+      <c r="C134">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>2020</v>
+      </c>
+      <c r="B135">
+        <v>10</v>
+      </c>
+      <c r="C135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>2020</v>
+      </c>
+      <c r="B136">
+        <v>11</v>
+      </c>
+      <c r="C136">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137">
+        <v>2020</v>
+      </c>
+      <c r="B137">
+        <v>12</v>
+      </c>
+      <c r="C137">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>2020</v>
+      </c>
+      <c r="B138">
+        <v>13</v>
+      </c>
+      <c r="C138">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>2020</v>
+      </c>
+      <c r="B139">
         <v>14</v>
       </c>
-      <c r="C134">
+      <c r="C139">
         <v>10</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -677,10 +677,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -710,24 +710,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -735,47 +726,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -794,23 +747,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -825,10 +779,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -840,8 +794,54 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -856,7 +856,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,25 +910,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -904,13 +952,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -922,121 +1024,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1047,24 +1047,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1086,34 +1068,41 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1133,16 +1122,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1155,145 +1155,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3993,7 +3993,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -4100,7 +4100,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>15</v>
@@ -4111,7 +4111,7 @@
         <v>30</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>15</v>
@@ -4122,7 +4122,7 @@
         <v>30</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>15</v>
@@ -4130,10 +4130,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -4144,7 +4144,7 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>15</v>
@@ -4155,7 +4155,7 @@
         <v>31</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>15</v>
@@ -4166,7 +4166,7 @@
         <v>31</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -4177,7 +4177,7 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>15</v>
@@ -4199,7 +4199,7 @@
         <v>32</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>15</v>
@@ -4210,7 +4210,7 @@
         <v>32</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>15</v>
@@ -4221,7 +4221,7 @@
         <v>32</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>15</v>
@@ -4232,7 +4232,7 @@
         <v>32</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>15</v>
@@ -4240,13 +4240,13 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4254,7 +4254,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -4265,7 +4265,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -4276,7 +4276,7 @@
         <v>33</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -4298,7 +4298,7 @@
         <v>40</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -4309,7 +4309,7 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -4320,7 +4320,7 @@
         <v>40</v>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -4342,7 +4342,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>10</v>
@@ -4353,7 +4353,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -4364,7 +4364,7 @@
         <v>41</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -4375,7 +4375,7 @@
         <v>41</v>
       </c>
       <c r="B35">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -4397,7 +4397,7 @@
         <v>42</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>10</v>
@@ -4408,7 +4408,7 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -4419,7 +4419,7 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C39">
         <v>10</v>
@@ -4430,29 +4430,29 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C40">
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" ht="28" customHeight="1" spans="1:3">
       <c r="A41">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B41">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>10</v>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1" spans="1:3">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>50</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>10</v>
@@ -4463,7 +4463,7 @@
         <v>50</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>10</v>
@@ -4474,7 +4474,7 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44">
         <v>10</v>
@@ -4485,21 +4485,21 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -4507,7 +4507,7 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -4518,7 +4518,7 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -4529,7 +4529,7 @@
         <v>51</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -4540,21 +4540,21 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -4562,7 +4562,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>10</v>
@@ -4573,7 +4573,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C53">
         <v>10</v>
@@ -4584,7 +4584,7 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C54">
         <v>10</v>
@@ -4595,21 +4595,21 @@
         <v>52</v>
       </c>
       <c r="B55">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B56">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -4617,7 +4617,7 @@
         <v>53</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>10</v>
@@ -4628,7 +4628,7 @@
         <v>53</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C58">
         <v>10</v>
@@ -4639,7 +4639,7 @@
         <v>53</v>
       </c>
       <c r="B59">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C59">
         <v>10</v>
@@ -4650,21 +4650,21 @@
         <v>53</v>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B61">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C61">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -4672,7 +4672,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C62">
         <v>10</v>
@@ -4683,7 +4683,7 @@
         <v>61</v>
       </c>
       <c r="B63">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C63">
         <v>10</v>
@@ -4691,10 +4691,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C64">
         <v>10</v>
@@ -4705,7 +4705,7 @@
         <v>62</v>
       </c>
       <c r="B65">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C65">
         <v>10</v>
@@ -4716,7 +4716,7 @@
         <v>62</v>
       </c>
       <c r="B66">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66">
         <v>10</v>
@@ -4724,10 +4724,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B67">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C67">
         <v>10</v>
@@ -4738,7 +4738,7 @@
         <v>63</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C68">
         <v>10</v>
@@ -4749,7 +4749,7 @@
         <v>63</v>
       </c>
       <c r="B69">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C69">
         <v>10</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>10</v>
@@ -4771,7 +4771,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>10</v>
@@ -4782,7 +4782,7 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C72">
         <v>10</v>
@@ -4793,7 +4793,7 @@
         <v>70</v>
       </c>
       <c r="B73">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C73">
         <v>10</v>
@@ -4804,7 +4804,7 @@
         <v>70</v>
       </c>
       <c r="B74">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -4815,7 +4815,7 @@
         <v>70</v>
       </c>
       <c r="B75">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C75">
         <v>10</v>
@@ -4826,7 +4826,7 @@
         <v>70</v>
       </c>
       <c r="B76">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76">
         <v>10</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -4848,7 +4848,7 @@
         <v>71</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C78">
         <v>10</v>
@@ -4859,7 +4859,7 @@
         <v>71</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C79">
         <v>10</v>
@@ -4870,7 +4870,7 @@
         <v>71</v>
       </c>
       <c r="B80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C80">
         <v>10</v>
@@ -4881,7 +4881,7 @@
         <v>71</v>
       </c>
       <c r="B81">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C81">
         <v>10</v>
@@ -4892,7 +4892,7 @@
         <v>71</v>
       </c>
       <c r="B82">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C82">
         <v>10</v>
@@ -4903,7 +4903,7 @@
         <v>71</v>
       </c>
       <c r="B83">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C83">
         <v>10</v>
@@ -4911,10 +4911,10 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B84">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C84">
         <v>10</v>
@@ -4925,7 +4925,7 @@
         <v>72</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C85">
         <v>10</v>
@@ -4936,7 +4936,7 @@
         <v>72</v>
       </c>
       <c r="B86">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -4947,7 +4947,7 @@
         <v>72</v>
       </c>
       <c r="B87">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C87">
         <v>10</v>
@@ -4958,7 +4958,7 @@
         <v>72</v>
       </c>
       <c r="B88">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C88">
         <v>10</v>
@@ -4969,7 +4969,7 @@
         <v>72</v>
       </c>
       <c r="B89">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C89">
         <v>10</v>
@@ -4977,10 +4977,10 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B90">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C90">
         <v>10</v>
@@ -4991,7 +4991,7 @@
         <v>73</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C91">
         <v>10</v>
@@ -5002,7 +5002,7 @@
         <v>73</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -5013,7 +5013,7 @@
         <v>73</v>
       </c>
       <c r="B93">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93">
         <v>10</v>
@@ -5024,7 +5024,7 @@
         <v>73</v>
       </c>
       <c r="B94">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C94">
         <v>10</v>
@@ -5035,7 +5035,7 @@
         <v>73</v>
       </c>
       <c r="B95">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C95">
         <v>10</v>
@@ -5046,7 +5046,7 @@
         <v>73</v>
       </c>
       <c r="B96">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C96">
         <v>10</v>
@@ -5054,13 +5054,13 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>73</v>
+        <v>1010</v>
       </c>
       <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
         <v>15</v>
-      </c>
-      <c r="C97">
-        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -5068,7 +5068,7 @@
         <v>1010</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98">
         <v>15</v>
@@ -5079,7 +5079,7 @@
         <v>1010</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C99">
         <v>15</v>
@@ -5090,7 +5090,7 @@
         <v>1010</v>
       </c>
       <c r="B100">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C100">
         <v>15</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B101">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C101">
         <v>15</v>
@@ -5112,7 +5112,7 @@
         <v>1020</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102">
         <v>15</v>
@@ -5123,7 +5123,7 @@
         <v>1020</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C103">
         <v>15</v>
@@ -5134,7 +5134,7 @@
         <v>1020</v>
       </c>
       <c r="B104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C104">
         <v>15</v>
@@ -5145,7 +5145,7 @@
         <v>1020</v>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C105">
         <v>15</v>
@@ -5153,10 +5153,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="B106">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C106">
         <v>15</v>
@@ -5167,7 +5167,7 @@
         <v>1030</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C107">
         <v>15</v>
@@ -5178,7 +5178,7 @@
         <v>1030</v>
       </c>
       <c r="B108">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C108">
         <v>15</v>
@@ -5186,10 +5186,10 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="B109">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C109">
         <v>15</v>
@@ -5200,7 +5200,7 @@
         <v>1040</v>
       </c>
       <c r="B110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C110">
         <v>15</v>
@@ -5211,7 +5211,7 @@
         <v>1040</v>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C111">
         <v>15</v>
@@ -5222,7 +5222,7 @@
         <v>1040</v>
       </c>
       <c r="B112">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -5233,7 +5233,7 @@
         <v>1040</v>
       </c>
       <c r="B113">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C113">
         <v>15</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="B114">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C114">
         <v>15</v>
@@ -5255,7 +5255,7 @@
         <v>1050</v>
       </c>
       <c r="B115">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C115">
         <v>15</v>
@@ -5266,7 +5266,7 @@
         <v>1050</v>
       </c>
       <c r="B116">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C116">
         <v>15</v>
@@ -5274,13 +5274,13 @@
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>1050</v>
+        <v>2010</v>
       </c>
       <c r="B117">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -5288,7 +5288,7 @@
         <v>2010</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118">
         <v>10</v>
@@ -5299,7 +5299,7 @@
         <v>2010</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C119">
         <v>10</v>
@@ -5310,7 +5310,7 @@
         <v>2010</v>
       </c>
       <c r="B120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C120">
         <v>10</v>
@@ -5321,7 +5321,7 @@
         <v>2010</v>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C121">
         <v>10</v>
@@ -5332,7 +5332,7 @@
         <v>2010</v>
       </c>
       <c r="B122">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -5343,7 +5343,7 @@
         <v>2010</v>
       </c>
       <c r="B123">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C123">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="B124">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>10</v>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="B125">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -5376,7 +5376,7 @@
         <v>2020</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -5387,7 +5387,7 @@
         <v>2020</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C127">
         <v>10</v>
@@ -5398,7 +5398,7 @@
         <v>2020</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C128">
         <v>10</v>
@@ -5409,7 +5409,7 @@
         <v>2020</v>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C129">
         <v>10</v>
@@ -5420,7 +5420,7 @@
         <v>2020</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C130">
         <v>10</v>
@@ -5431,7 +5431,7 @@
         <v>2020</v>
       </c>
       <c r="B131">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C131">
         <v>10</v>
@@ -5442,7 +5442,7 @@
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C132">
         <v>10</v>
@@ -5453,7 +5453,7 @@
         <v>2020</v>
       </c>
       <c r="B133">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C133">
         <v>10</v>
@@ -5464,7 +5464,7 @@
         <v>2020</v>
       </c>
       <c r="B134">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C134">
         <v>10</v>
@@ -5475,7 +5475,7 @@
         <v>2020</v>
       </c>
       <c r="B135">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C135">
         <v>10</v>
@@ -5486,7 +5486,7 @@
         <v>2020</v>
       </c>
       <c r="B136">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C136">
         <v>10</v>
@@ -5497,31 +5497,9 @@
         <v>2020</v>
       </c>
       <c r="B137">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C137">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138">
-        <v>2020</v>
-      </c>
-      <c r="B138">
-        <v>13</v>
-      </c>
-      <c r="C138">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
-      <c r="A139">
-        <v>2020</v>
-      </c>
-      <c r="B139">
-        <v>14</v>
-      </c>
-      <c r="C139">
         <v>10</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -678,9 +678,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -717,62 +717,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -787,22 +741,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -811,21 +750,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -846,6 +770,82 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -862,79 +862,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -946,61 +880,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1018,7 +904,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1030,13 +1018,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1047,6 +1047,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1061,48 +1076,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1147,6 +1120,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1155,145 +1155,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3574,7 +3574,7 @@
         <v>3</v>
       </c>
       <c r="G32">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -4012,7 +4012,7 @@
         <v>20</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -4023,7 +4023,7 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -4034,7 +4034,7 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -4045,7 +4045,7 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -4056,7 +4056,7 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -4067,7 +4067,7 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -4078,7 +4078,7 @@
         <v>21</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>15</v>
@@ -4246,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -4257,7 +4257,7 @@
         <v>3</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -4268,7 +4268,7 @@
         <v>4</v>
       </c>
       <c r="C25">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -4279,7 +4279,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -5057,7 +5057,7 @@
         <v>1010</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
         <v>15</v>
@@ -5068,7 +5068,7 @@
         <v>1010</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>15</v>
@@ -5090,7 +5090,7 @@
         <v>1010</v>
       </c>
       <c r="B100">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C100">
         <v>15</v>
@@ -5343,7 +5343,7 @@
         <v>2010</v>
       </c>
       <c r="B123">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C123">
         <v>10</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,9 @@
     <sheet name="TextData" sheetId="5" r:id="rId5"/>
     <sheet name="Define" sheetId="6" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StageEvents!$F$1:$F$21</definedName>
   </definedNames>
@@ -22,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="208">
   <si>
     <t>Id</t>
   </si>
@@ -166,6 +169,9 @@
   </si>
   <si>
     <t>Weight</t>
+  </si>
+  <si>
+    <t>LineIndex</t>
   </si>
   <si>
     <t>Turns</t>
@@ -677,10 +683,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -704,29 +710,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -741,7 +725,82 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -757,67 +816,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -832,18 +838,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -856,7 +862,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +892,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,7 +910,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,13 +976,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -910,85 +1030,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,43 +1042,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1050,16 +1056,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1080,17 +1101,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1106,30 +1130,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1139,11 +1139,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1155,25 +1161,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1182,118 +1188,118 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1372,6 +1378,388 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Enemies"/>
+      <sheetName val="Learning"/>
+      <sheetName val="Triggers"/>
+      <sheetName val="TextData"/>
+      <sheetName val="Define"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Id</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>Text</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>ネレイドジェム</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>カースド</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>ビー</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>ウルフ</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>クロウ</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>ゴーストアーマー</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>サーチャー</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>シールド</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>ドライアド</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>スコーピオン</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>スクイッド</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>ネームレス</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>インプ</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>クリーパー</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>ソード</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>51</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>オーガ</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>101</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>アンドラス</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>102</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>ベリト</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>103</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>パイモン</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>104</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>アモン</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>105</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>ビフロンス</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>106</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>アイホート</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>107</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>ビヤーキー</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>201</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>ファフニール</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>202</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>ザガン</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>203</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>アスタロト</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>204</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>デカラビア</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>205</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>インドラ</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>206</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>ズルワーン</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>207</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>アンリマユ</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>301</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>デビルドラゴン</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>1001</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>ミカ</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>1002</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>エリザベート</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>1003</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>アリエス</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>1004</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>シイナ</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>1005</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>レダ</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>1006</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>リシェリ</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>1007</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>ユニ</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>1008</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>マリーベル</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>1009</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>ナツキ</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>1010</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>メリアドール</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>1011</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>セリナ</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>1101</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>シグルド</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>1102</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>ブリュンヒルデ</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2160,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -2172,10 +2560,10 @@
         <v>30</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -2222,22 +2610,22 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>30</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -2284,22 +2672,22 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>30</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -2414,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>30</v>
@@ -2476,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -2538,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>30</v>
@@ -2600,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -2724,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>30</v>
@@ -2786,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>30</v>
@@ -2848,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>30</v>
@@ -2910,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -3993,10 +4381,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C137"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:E136"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
+  <cols>
+    <col min="4" max="4" width="9.45454545454546" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4006,8 +4397,11 @@
       <c r="C1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>20</v>
       </c>
@@ -4017,8 +4411,15 @@
       <c r="C2">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>-1</v>
+      </c>
+      <c r="E2" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B2,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>20</v>
       </c>
@@ -4028,8 +4429,15 @@
       <c r="C3">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>-1</v>
+      </c>
+      <c r="E3" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B3,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>20</v>
       </c>
@@ -4039,8 +4447,15 @@
       <c r="C4">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>-1</v>
+      </c>
+      <c r="E4" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B4,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>21</v>
       </c>
@@ -4050,8 +4465,15 @@
       <c r="C5">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="E5" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B5,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>21</v>
       </c>
@@ -4061,8 +4483,15 @@
       <c r="C6">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="E6" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B6,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>21</v>
       </c>
@@ -4072,8 +4501,15 @@
       <c r="C7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B7,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>21</v>
       </c>
@@ -4083,8 +4519,15 @@
       <c r="C8">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>-1</v>
+      </c>
+      <c r="E8" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B8,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>30</v>
       </c>
@@ -4094,8 +4537,15 @@
       <c r="C9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>-1</v>
+      </c>
+      <c r="E9" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B9,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>30</v>
       </c>
@@ -4105,8 +4555,15 @@
       <c r="C10">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B10,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>30</v>
       </c>
@@ -4116,8 +4573,15 @@
       <c r="C11">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <v>-1</v>
+      </c>
+      <c r="E11" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B11,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>30</v>
       </c>
@@ -4127,8 +4591,15 @@
       <c r="C12">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <v>-1</v>
+      </c>
+      <c r="E12" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B12,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>31</v>
       </c>
@@ -4138,8 +4609,15 @@
       <c r="C13">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13">
+        <v>-1</v>
+      </c>
+      <c r="E13" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B13,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>31</v>
       </c>
@@ -4149,8 +4627,15 @@
       <c r="C14">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <v>-1</v>
+      </c>
+      <c r="E14" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B14,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>31</v>
       </c>
@@ -4160,8 +4645,15 @@
       <c r="C15">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <v>-1</v>
+      </c>
+      <c r="E15" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B15,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>31</v>
       </c>
@@ -4171,8 +4663,15 @@
       <c r="C16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>-1</v>
+      </c>
+      <c r="E16" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B16,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>31</v>
       </c>
@@ -4182,8 +4681,15 @@
       <c r="C17">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>-1</v>
+      </c>
+      <c r="E17" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B17,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>32</v>
       </c>
@@ -4193,8 +4699,15 @@
       <c r="C18">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <v>-1</v>
+      </c>
+      <c r="E18" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B18,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>32</v>
       </c>
@@ -4204,8 +4717,15 @@
       <c r="C19">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>-1</v>
+      </c>
+      <c r="E19" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B19,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>32</v>
       </c>
@@ -4215,8 +4735,15 @@
       <c r="C20">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>-1</v>
+      </c>
+      <c r="E20" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B20,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>32</v>
       </c>
@@ -4226,8 +4753,15 @@
       <c r="C21">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <v>-1</v>
+      </c>
+      <c r="E21" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B21,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>32</v>
       </c>
@@ -4237,8 +4771,15 @@
       <c r="C22">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <v>-1</v>
+      </c>
+      <c r="E22" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B22,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>33</v>
       </c>
@@ -4248,8 +4789,15 @@
       <c r="C23">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <v>-1</v>
+      </c>
+      <c r="E23" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B23,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>33</v>
       </c>
@@ -4259,8 +4807,15 @@
       <c r="C24">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <v>-1</v>
+      </c>
+      <c r="E24" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B24,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>33</v>
       </c>
@@ -4270,8 +4825,15 @@
       <c r="C25">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25">
+        <v>-1</v>
+      </c>
+      <c r="E25" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B25,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>33</v>
       </c>
@@ -4281,41 +4843,69 @@
       <c r="C26">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <v>-1</v>
+      </c>
+      <c r="E26" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B26,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>40</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27">
+        <v>-1</v>
+      </c>
+      <c r="E27" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B27,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>40</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28">
+        <v>-1</v>
+      </c>
+      <c r="E28" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B28,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>40</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29">
+        <v>-1</v>
+      </c>
+      <c r="E29" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B29,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>40</v>
       </c>
@@ -4325,8 +4915,15 @@
       <c r="C30">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30">
+        <v>-1</v>
+      </c>
+      <c r="E30" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B30,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>41</v>
       </c>
@@ -4336,8 +4933,15 @@
       <c r="C31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31">
+        <v>-1</v>
+      </c>
+      <c r="E31" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B31,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>41</v>
       </c>
@@ -4347,8 +4951,15 @@
       <c r="C32">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32">
+        <v>-1</v>
+      </c>
+      <c r="E32" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B32,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>41</v>
       </c>
@@ -4358,52 +4969,87 @@
       <c r="C33">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33">
+        <v>-1</v>
+      </c>
+      <c r="E33" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B33,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>41</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34">
+        <v>-1</v>
+      </c>
+      <c r="E34" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B34,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>10</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35">
+        <v>-1</v>
+      </c>
+      <c r="E35" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B35,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>42</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36">
+        <v>-1</v>
+      </c>
+      <c r="E36" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B36,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37">
+        <v>-1</v>
+      </c>
+      <c r="E37" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B37,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>42</v>
       </c>
@@ -4413,1094 +5059,1776 @@
       <c r="C38">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38">
+        <v>-1</v>
+      </c>
+      <c r="E38" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B38,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>42</v>
       </c>
       <c r="B39">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C39">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39">
+        <v>-1</v>
+      </c>
+      <c r="E39" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B39,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B40">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C40">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:3">
+      <c r="D40">
+        <v>-1</v>
+      </c>
+      <c r="E40" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B40,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>50</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41">
+        <v>-1</v>
+      </c>
+      <c r="E41" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B41,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>50</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42">
+        <v>-1</v>
+      </c>
+      <c r="E42" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B42,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>50</v>
       </c>
       <c r="B43">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43">
+        <v>-1</v>
+      </c>
+      <c r="E43" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B43,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>50</v>
       </c>
       <c r="B44">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D44">
+        <v>-1</v>
+      </c>
+      <c r="E44" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B44,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D45">
+        <v>-1</v>
+      </c>
+      <c r="E45" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B45,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>51</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46">
+        <v>-1</v>
+      </c>
+      <c r="E46" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B46,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>51</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47">
+        <v>-1</v>
+      </c>
+      <c r="E47" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B47,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>51</v>
       </c>
       <c r="B48">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C48">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48">
+        <v>-1</v>
+      </c>
+      <c r="E48" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B48,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>51</v>
       </c>
       <c r="B49">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C49">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D49">
+        <v>-1</v>
+      </c>
+      <c r="E49" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B49,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D50">
+        <v>-1</v>
+      </c>
+      <c r="E50" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B50,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>52</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51">
+        <v>-1</v>
+      </c>
+      <c r="E51" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B51,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>52</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C52">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52">
+        <v>-1</v>
+      </c>
+      <c r="E52" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B52,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C53">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53">
+        <v>-1</v>
+      </c>
+      <c r="E53" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B53,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C54">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D54">
+        <v>-1</v>
+      </c>
+      <c r="E54" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B54,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D55">
+        <v>-1</v>
+      </c>
+      <c r="E55" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B55,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>53</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56">
+        <v>-1</v>
+      </c>
+      <c r="E56" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B56,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>53</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C57">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57">
+        <v>-1</v>
+      </c>
+      <c r="E57" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B57,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>53</v>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C58">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58">
+        <v>-1</v>
+      </c>
+      <c r="E58" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B58,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>53</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C59">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D59">
+        <v>-1</v>
+      </c>
+      <c r="E59" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B59,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B60">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D60">
+        <v>-1</v>
+      </c>
+      <c r="E60" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B60,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>61</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C61">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61">
+        <v>-1</v>
+      </c>
+      <c r="E61" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B61,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C62">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62">
+        <v>-1</v>
+      </c>
+      <c r="E62" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B62,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C63">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63">
+        <v>-1</v>
+      </c>
+      <c r="E63" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B63,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C64">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64">
+        <v>-1</v>
+      </c>
+      <c r="E64" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B64,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>62</v>
       </c>
       <c r="B65">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C65">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65">
+        <v>-1</v>
+      </c>
+      <c r="E65" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B65,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B66">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C66">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66">
+        <v>-1</v>
+      </c>
+      <c r="E66" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B66,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>63</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C67">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67">
+        <v>-1</v>
+      </c>
+      <c r="E67" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B67,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>63</v>
       </c>
       <c r="B68">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="D68">
+        <v>-1</v>
+      </c>
+      <c r="E68" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B68,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B69">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C69">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69">
+        <v>-1</v>
+      </c>
+      <c r="E69" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B69,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>70</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>10</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70">
+        <v>-1</v>
+      </c>
+      <c r="E70" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B70,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C71">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71">
+        <v>-1</v>
+      </c>
+      <c r="E71" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B71,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>70</v>
       </c>
       <c r="B72">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C72">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72">
+        <v>-1</v>
+      </c>
+      <c r="E72" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B72,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>70</v>
       </c>
       <c r="B73">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="D73">
+        <v>-1</v>
+      </c>
+      <c r="E73" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B73,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>70</v>
       </c>
       <c r="B74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C74">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="D74">
+        <v>-1</v>
+      </c>
+      <c r="E74" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B74,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>70</v>
       </c>
       <c r="B75">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C75">
         <v>10</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75">
+        <v>-1</v>
+      </c>
+      <c r="E75" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B75,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B76">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76">
+        <v>-1</v>
+      </c>
+      <c r="E76" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B76,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>71</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C77">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="D77">
+        <v>-1</v>
+      </c>
+      <c r="E77" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B77,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>71</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C78">
         <v>10</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="D78">
+        <v>-1</v>
+      </c>
+      <c r="E78" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>71</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C79">
         <v>10</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="D79">
+        <v>-1</v>
+      </c>
+      <c r="E79" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>71</v>
       </c>
       <c r="B80">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C80">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D80">
+        <v>-1</v>
+      </c>
+      <c r="E80" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>71</v>
       </c>
       <c r="B81">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C81">
         <v>10</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81">
+        <v>-1</v>
+      </c>
+      <c r="E81" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>71</v>
       </c>
       <c r="B82">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C82">
         <v>10</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82">
+        <v>-1</v>
+      </c>
+      <c r="E82" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B83">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C83">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83">
+        <v>-1</v>
+      </c>
+      <c r="E83" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>72</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C84">
         <v>10</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84">
+        <v>-1</v>
+      </c>
+      <c r="E84" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>72</v>
       </c>
       <c r="B85">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C85">
         <v>10</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85">
+        <v>-1</v>
+      </c>
+      <c r="E85" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>72</v>
       </c>
       <c r="B86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C86">
         <v>10</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="D86">
+        <v>-1</v>
+      </c>
+      <c r="E86" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>72</v>
       </c>
       <c r="B87">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C87">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="D87">
+        <v>-1</v>
+      </c>
+      <c r="E87" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>72</v>
       </c>
       <c r="B88">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88">
         <v>10</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="D88">
+        <v>-1</v>
+      </c>
+      <c r="E88" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="D89">
+        <v>-1</v>
+      </c>
+      <c r="E89" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>73</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>10</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="D90">
+        <v>-1</v>
+      </c>
+      <c r="E90" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>73</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C91">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="D91">
+        <v>-1</v>
+      </c>
+      <c r="E91" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>73</v>
       </c>
       <c r="B92">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92">
         <v>10</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="D92">
+        <v>-1</v>
+      </c>
+      <c r="E92" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>73</v>
       </c>
       <c r="B93">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C93">
         <v>10</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="D93">
+        <v>-1</v>
+      </c>
+      <c r="E93" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>73</v>
       </c>
       <c r="B94">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C94">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="D94">
+        <v>-1</v>
+      </c>
+      <c r="E94" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>73</v>
       </c>
       <c r="B95">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C95">
         <v>10</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="D95">
+        <v>-1</v>
+      </c>
+      <c r="E95" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96">
-        <v>73</v>
+        <v>1010</v>
       </c>
       <c r="B96">
+        <v>3</v>
+      </c>
+      <c r="C96">
         <v>15</v>
       </c>
-      <c r="C96">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="D96">
+        <v>-1</v>
+      </c>
+      <c r="E96" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>1010</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C97">
         <v>15</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="D97">
+        <v>-1</v>
+      </c>
+      <c r="E97" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>1010</v>
       </c>
       <c r="B98">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C98">
         <v>15</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="D98">
+        <v>-1</v>
+      </c>
+      <c r="E98" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>1010</v>
       </c>
       <c r="B99">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C99">
         <v>15</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="D99">
+        <v>-1</v>
+      </c>
+      <c r="E99" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="B100">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C100">
         <v>15</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="D100">
+        <v>-1</v>
+      </c>
+      <c r="E100" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>1020</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C101">
         <v>15</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="D101">
+        <v>-1</v>
+      </c>
+      <c r="E101" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>1020</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C102">
         <v>15</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="D102">
+        <v>-1</v>
+      </c>
+      <c r="E102" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>1020</v>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C103">
         <v>15</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="D103">
+        <v>-1</v>
+      </c>
+      <c r="E103" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>1020</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C104">
         <v>15</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="D104">
+        <v>-1</v>
+      </c>
+      <c r="E104" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="B105">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>15</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
+      <c r="D105">
+        <v>-1</v>
+      </c>
+      <c r="E105" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>1030</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C106">
         <v>15</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="D106">
+        <v>-1</v>
+      </c>
+      <c r="E106" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>1030</v>
       </c>
       <c r="B107">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C107">
         <v>15</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="D107">
+        <v>-1</v>
+      </c>
+      <c r="E107" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="B108">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C108">
         <v>15</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
+      <c r="D108">
+        <v>-1</v>
+      </c>
+      <c r="E108" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>1040</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C109">
         <v>15</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="D109">
+        <v>-1</v>
+      </c>
+      <c r="E109" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>1040</v>
       </c>
       <c r="B110">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C110">
         <v>15</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="D110">
+        <v>-1</v>
+      </c>
+      <c r="E110" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>1040</v>
       </c>
       <c r="B111">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C111">
         <v>15</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="D111">
+        <v>-1</v>
+      </c>
+      <c r="E111" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112">
         <v>1040</v>
       </c>
       <c r="B112">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C112">
         <v>15</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="D112">
+        <v>-1</v>
+      </c>
+      <c r="E112" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="B113">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C113">
         <v>15</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="D113">
+        <v>-1</v>
+      </c>
+      <c r="E113" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114">
         <v>1050</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C114">
         <v>15</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="D114">
+        <v>-1</v>
+      </c>
+      <c r="E114" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>1050</v>
       </c>
       <c r="B115">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C115">
         <v>15</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="D115">
+        <v>-1</v>
+      </c>
+      <c r="E115" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116">
-        <v>1050</v>
+        <v>2010</v>
       </c>
       <c r="B116">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D116">
+        <v>-1</v>
+      </c>
+      <c r="E116" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>2010</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117">
         <v>10</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="D117">
+        <v>-1</v>
+      </c>
+      <c r="E117" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>2010</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>10</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
+      <c r="D118">
+        <v>-1</v>
+      </c>
+      <c r="E118" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>2010</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C119">
         <v>10</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
+      <c r="D119">
+        <v>-1</v>
+      </c>
+      <c r="E119" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>2010</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C120">
         <v>10</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
+      <c r="D120">
+        <v>-1</v>
+      </c>
+      <c r="E120" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>2010</v>
       </c>
       <c r="B121">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C121">
         <v>10</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
+      <c r="D121">
+        <v>-1</v>
+      </c>
+      <c r="E121" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>2010</v>
       </c>
       <c r="B122">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C122">
         <v>10</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
+      <c r="D122">
+        <v>-1</v>
+      </c>
+      <c r="E122" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="B123">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C123">
         <v>10</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
+      <c r="D123">
+        <v>-1</v>
+      </c>
+      <c r="E123" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124">
         <v>2020</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>10</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="D124">
+        <v>-1</v>
+      </c>
+      <c r="E124" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125">
         <v>2020</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C125">
         <v>10</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
+      <c r="D125">
+        <v>-1</v>
+      </c>
+      <c r="E125" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126">
         <v>2020</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C126">
         <v>10</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
+      <c r="D126">
+        <v>-1</v>
+      </c>
+      <c r="E126" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127">
         <v>2020</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C127">
         <v>10</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
+      <c r="D127">
+        <v>-1</v>
+      </c>
+      <c r="E127" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128">
         <v>2020</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C128">
         <v>10</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
+      <c r="D128">
+        <v>-1</v>
+      </c>
+      <c r="E128" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129">
         <v>2020</v>
       </c>
       <c r="B129">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C129">
         <v>10</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
+      <c r="D129">
+        <v>-1</v>
+      </c>
+      <c r="E129" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130">
         <v>2020</v>
       </c>
       <c r="B130">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C130">
         <v>10</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="D130">
+        <v>-1</v>
+      </c>
+      <c r="E130" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131">
         <v>2020</v>
       </c>
       <c r="B131">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C131">
         <v>10</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
+      <c r="D131">
+        <v>-1</v>
+      </c>
+      <c r="E131" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132">
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C132">
         <v>10</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
+      <c r="D132">
+        <v>-1</v>
+      </c>
+      <c r="E132" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133">
         <v>2020</v>
       </c>
       <c r="B133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C133">
         <v>10</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="D133">
+        <v>-1</v>
+      </c>
+      <c r="E133" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134">
         <v>2020</v>
       </c>
       <c r="B134">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C134">
         <v>10</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
+      <c r="D134">
+        <v>-1</v>
+      </c>
+      <c r="E134" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135">
         <v>2020</v>
       </c>
       <c r="B135">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C135">
         <v>10</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="D135">
+        <v>-1</v>
+      </c>
+      <c r="E135" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136">
         <v>2020</v>
       </c>
       <c r="B136">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C136">
         <v>10</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137">
-        <v>2020</v>
-      </c>
-      <c r="B137">
-        <v>14</v>
-      </c>
-      <c r="C137">
-        <v>10</v>
+      <c r="D136">
+        <v>-1</v>
+      </c>
+      <c r="E136" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
       </c>
     </row>
   </sheetData>
@@ -5520,25 +6848,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
         <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5592,16 +6920,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5609,13 +6937,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>21</v>
@@ -5626,13 +6954,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -5643,16 +6971,16 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5660,13 +6988,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -5677,16 +7005,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5694,13 +7022,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -5711,13 +7039,13 @@
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -5728,13 +7056,13 @@
         <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -5745,16 +7073,16 @@
         <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5762,13 +7090,13 @@
         <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
@@ -5779,13 +7107,13 @@
         <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -5796,16 +7124,16 @@
         <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5813,13 +7141,13 @@
         <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
@@ -5830,13 +7158,13 @@
         <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
@@ -5847,13 +7175,13 @@
         <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -5864,13 +7192,13 @@
         <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
@@ -5881,16 +7209,16 @@
         <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5898,13 +7226,13 @@
         <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
@@ -5915,13 +7243,13 @@
         <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -5932,13 +7260,13 @@
         <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -5949,13 +7277,13 @@
         <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
@@ -5966,16 +7294,16 @@
         <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -5983,13 +7311,13 @@
         <v>71</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -6000,13 +7328,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -6017,13 +7345,13 @@
         <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -6034,13 +7362,13 @@
         <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
@@ -6051,16 +7379,16 @@
         <v>1010</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" ht="25" spans="1:7">
@@ -6068,16 +7396,16 @@
         <v>1020</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" ht="25" spans="1:7">
@@ -6085,16 +7413,16 @@
         <v>1030</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" ht="25" spans="1:7">
@@ -6102,16 +7430,16 @@
         <v>1040</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" ht="25" spans="1:7">
@@ -6119,16 +7447,16 @@
         <v>1050</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" ht="37.5" spans="1:7">
@@ -6136,16 +7464,16 @@
         <v>2010</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" ht="37.5" spans="1:7">
@@ -6153,16 +7481,16 @@
         <v>2020</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="35" ht="37.5" spans="1:7">
@@ -6170,16 +7498,16 @@
         <v>2030</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="36" spans="3:4">
@@ -6217,13 +7545,13 @@
         <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -6231,31 +7559,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -6263,34 +7591,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -6298,34 +7626,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D4">
         <v>1020</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -6333,34 +7661,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D5">
         <v>1030</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -6368,34 +7696,34 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D6">
         <v>2010</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -6403,34 +7731,34 @@
         <v>3010</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D7">
         <v>2011</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -6438,28 +7766,28 @@
         <v>2020</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -6467,28 +7795,28 @@
         <v>2021</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -6496,28 +7824,28 @@
         <v>2030</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -6525,19 +7853,19 @@
         <v>3010</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -6545,19 +7873,19 @@
         <v>3020</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -6565,19 +7893,19 @@
         <v>3030</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -6585,13 +7913,13 @@
         <v>4010</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -6599,7 +7927,7 @@
         <v>4011</v>
       </c>
       <c r="E15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -6607,7 +7935,7 @@
         <v>4020</v>
       </c>
       <c r="E16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -6615,7 +7943,7 @@
         <v>5010</v>
       </c>
       <c r="E17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -6623,7 +7951,7 @@
         <v>5020</v>
       </c>
       <c r="E18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -6631,7 +7959,7 @@
         <v>6010</v>
       </c>
       <c r="E19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -6639,7 +7967,7 @@
         <v>6011</v>
       </c>
       <c r="E20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -6647,7 +7975,7 @@
         <v>6020</v>
       </c>
       <c r="E21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -6655,7 +7983,7 @@
         <v>6030</v>
       </c>
       <c r="E22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -6663,7 +7991,7 @@
         <v>7010</v>
       </c>
       <c r="E23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -6671,7 +7999,7 @@
         <v>7020</v>
       </c>
       <c r="E24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -6679,7 +8007,7 @@
         <v>7021</v>
       </c>
       <c r="E25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -6687,7 +8015,7 @@
         <v>8010</v>
       </c>
       <c r="E26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -6695,7 +8023,7 @@
         <v>9010</v>
       </c>
       <c r="E27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -683,9 +683,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
@@ -716,21 +716,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -739,10 +724,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -754,31 +739,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -800,7 +794,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -808,33 +817,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -847,7 +847,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -868,7 +868,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,13 +922,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,67 +1012,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -970,79 +1036,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,6 +1053,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1067,6 +1091,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1086,59 +1130,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1153,6 +1144,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1161,145 +1161,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2684,10 +2684,10 @@
         <v>30</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -4381,7 +4381,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.45454545454546" customWidth="1"/>
@@ -5003,10 +5003,10 @@
         <v>1</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B35,[1]TextData!A:A))</f>
@@ -5021,10 +5021,10 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B36,[1]TextData!A:A))</f>
@@ -5039,10 +5039,10 @@
         <v>4</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B37,[1]TextData!A:A))</f>
@@ -5057,10 +5057,10 @@
         <v>9</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B38,[1]TextData!A:A))</f>
@@ -5072,35 +5072,35 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B39,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B40,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -5108,7 +5108,7 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>10</v>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="E41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B41,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5126,7 +5126,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>10</v>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="E42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B42,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -5144,7 +5144,7 @@
         <v>50</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="E43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B43,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -5162,35 +5162,35 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <v>-1</v>
       </c>
       <c r="E44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B44,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>-1</v>
       </c>
       <c r="E45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B45,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -5198,7 +5198,7 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46">
         <v>10</v>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="E46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B46,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -5216,7 +5216,7 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="E47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B47,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5234,7 +5234,7 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="E48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B48,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5252,35 +5252,35 @@
         <v>51</v>
       </c>
       <c r="B49">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D49">
         <v>-1</v>
       </c>
       <c r="E49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B49,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D50">
         <v>-1</v>
       </c>
       <c r="E50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B50,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -5288,7 +5288,7 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>10</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="E51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B51,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -5306,7 +5306,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>10</v>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B52,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5324,7 +5324,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C53">
         <v>10</v>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E53" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B53,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -5342,35 +5342,35 @@
         <v>52</v>
       </c>
       <c r="B54">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C54">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D54">
         <v>-1</v>
       </c>
       <c r="E54" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B54,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D55">
         <v>-1</v>
       </c>
       <c r="E55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B55,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -5378,7 +5378,7 @@
         <v>53</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>10</v>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B56,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -5396,7 +5396,7 @@
         <v>53</v>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>10</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B57,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -5414,7 +5414,7 @@
         <v>53</v>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58">
         <v>10</v>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="E58" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B58,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -5432,35 +5432,35 @@
         <v>53</v>
       </c>
       <c r="B59">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C59">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D59">
         <v>-1</v>
       </c>
       <c r="E59" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B59,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D60">
         <v>-1</v>
       </c>
       <c r="E60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B60,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -5468,7 +5468,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C61">
         <v>10</v>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="E61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B61,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -5486,7 +5486,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C62">
         <v>10</v>
@@ -5496,15 +5496,15 @@
       </c>
       <c r="E62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B62,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C63">
         <v>10</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B63,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -5522,7 +5522,7 @@
         <v>62</v>
       </c>
       <c r="B64">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C64">
         <v>10</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="E64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B64,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -5540,7 +5540,7 @@
         <v>62</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C65">
         <v>10</v>
@@ -5550,15 +5550,15 @@
       </c>
       <c r="E65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B65,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C66">
         <v>10</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="E66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B66,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -5576,7 +5576,7 @@
         <v>63</v>
       </c>
       <c r="B67">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C67">
         <v>10</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="E67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B67,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -5594,7 +5594,7 @@
         <v>63</v>
       </c>
       <c r="B68">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C68">
         <v>10</v>
@@ -5604,15 +5604,15 @@
       </c>
       <c r="E68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B68,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C69">
         <v>10</v>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="E69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B69,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -5630,7 +5630,7 @@
         <v>70</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>10</v>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B70,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -5648,7 +5648,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>10</v>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B71,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -5666,7 +5666,7 @@
         <v>70</v>
       </c>
       <c r="B72">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C72">
         <v>10</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B72,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -5684,7 +5684,7 @@
         <v>70</v>
       </c>
       <c r="B73">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73">
         <v>10</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="E73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B73,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -5702,7 +5702,7 @@
         <v>70</v>
       </c>
       <c r="B74">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="E74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B74,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -5720,7 +5720,7 @@
         <v>70</v>
       </c>
       <c r="B75">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75">
         <v>10</v>
@@ -5730,15 +5730,15 @@
       </c>
       <c r="E75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B75,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C76">
         <v>10</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B76,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -5756,7 +5756,7 @@
         <v>71</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="E77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B77,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -5774,7 +5774,7 @@
         <v>71</v>
       </c>
       <c r="B78">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C78">
         <v>10</v>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="E78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -5792,7 +5792,7 @@
         <v>71</v>
       </c>
       <c r="B79">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79">
         <v>10</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="E79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -5810,7 +5810,7 @@
         <v>71</v>
       </c>
       <c r="B80">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C80">
         <v>10</v>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -5828,7 +5828,7 @@
         <v>71</v>
       </c>
       <c r="B81">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C81">
         <v>10</v>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="E81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -5846,7 +5846,7 @@
         <v>71</v>
       </c>
       <c r="B82">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C82">
         <v>10</v>
@@ -5856,15 +5856,15 @@
       </c>
       <c r="E82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C83">
         <v>10</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="E83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -5882,7 +5882,7 @@
         <v>72</v>
       </c>
       <c r="B84">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C84">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="E84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -5900,7 +5900,7 @@
         <v>72</v>
       </c>
       <c r="B85">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C85">
         <v>10</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -5918,7 +5918,7 @@
         <v>72</v>
       </c>
       <c r="B86">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="E86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -5936,7 +5936,7 @@
         <v>72</v>
       </c>
       <c r="B87">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87">
         <v>10</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -5954,7 +5954,7 @@
         <v>72</v>
       </c>
       <c r="B88">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88">
         <v>10</v>
@@ -5964,15 +5964,15 @@
       </c>
       <c r="E88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C89">
         <v>10</v>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="E89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -5990,7 +5990,7 @@
         <v>73</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C90">
         <v>10</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="E90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -6008,7 +6008,7 @@
         <v>73</v>
       </c>
       <c r="B91">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C91">
         <v>10</v>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -6026,7 +6026,7 @@
         <v>73</v>
       </c>
       <c r="B92">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="E92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -6044,7 +6044,7 @@
         <v>73</v>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C93">
         <v>10</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="E93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -6062,7 +6062,7 @@
         <v>73</v>
       </c>
       <c r="B94">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C94">
         <v>10</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="E94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -6080,7 +6080,7 @@
         <v>73</v>
       </c>
       <c r="B95">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C95">
         <v>10</v>
@@ -6090,25 +6090,25 @@
       </c>
       <c r="E95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C96">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D96">
         <v>-1</v>
       </c>
       <c r="E96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -6116,7 +6116,7 @@
         <v>1010</v>
       </c>
       <c r="B97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C97">
         <v>15</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="E97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -6134,7 +6134,7 @@
         <v>1010</v>
       </c>
       <c r="B98">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>15</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="E98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -6152,7 +6152,7 @@
         <v>1010</v>
       </c>
       <c r="B99">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C99">
         <v>15</v>
@@ -6162,15 +6162,15 @@
       </c>
       <c r="E99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C100">
         <v>15</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="E100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -6188,7 +6188,7 @@
         <v>1020</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
         <v>15</v>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -6206,7 +6206,7 @@
         <v>1020</v>
       </c>
       <c r="B102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C102">
         <v>15</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="E102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -6224,7 +6224,7 @@
         <v>1020</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103">
         <v>15</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -6242,7 +6242,7 @@
         <v>1020</v>
       </c>
       <c r="B104">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C104">
         <v>15</v>
@@ -6252,15 +6252,15 @@
       </c>
       <c r="E104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C105">
         <v>15</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="E105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -6278,7 +6278,7 @@
         <v>1030</v>
       </c>
       <c r="B106">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C106">
         <v>15</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="E106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -6296,7 +6296,7 @@
         <v>1030</v>
       </c>
       <c r="B107">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C107">
         <v>15</v>
@@ -6306,15 +6306,15 @@
       </c>
       <c r="E107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C108">
         <v>15</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="E108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -6332,7 +6332,7 @@
         <v>1040</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109">
         <v>15</v>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="E109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -6350,7 +6350,7 @@
         <v>1040</v>
       </c>
       <c r="B110">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C110">
         <v>15</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="E110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -6368,7 +6368,7 @@
         <v>1040</v>
       </c>
       <c r="B111">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C111">
         <v>15</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="E111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -6386,7 +6386,7 @@
         <v>1040</v>
       </c>
       <c r="B112">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -6396,15 +6396,15 @@
       </c>
       <c r="E112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C113">
         <v>15</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="E113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -6422,7 +6422,7 @@
         <v>1050</v>
       </c>
       <c r="B114">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C114">
         <v>15</v>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="E114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -6440,7 +6440,7 @@
         <v>1050</v>
       </c>
       <c r="B115">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C115">
         <v>15</v>
@@ -6450,25 +6450,25 @@
       </c>
       <c r="E115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C116">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D116">
         <v>-1</v>
       </c>
       <c r="E116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -6476,7 +6476,7 @@
         <v>2010</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117">
         <v>10</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -6494,7 +6494,7 @@
         <v>2010</v>
       </c>
       <c r="B118">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C118">
         <v>10</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -6512,7 +6512,7 @@
         <v>2010</v>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119">
         <v>10</v>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="E119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -6530,7 +6530,7 @@
         <v>2010</v>
       </c>
       <c r="B120">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C120">
         <v>10</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -6548,7 +6548,7 @@
         <v>2010</v>
       </c>
       <c r="B121">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C121">
         <v>10</v>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="E121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -6566,7 +6566,7 @@
         <v>2010</v>
       </c>
       <c r="B122">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -6576,15 +6576,15 @@
       </c>
       <c r="E122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C123">
         <v>10</v>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="E123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -6602,7 +6602,7 @@
         <v>2020</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>10</v>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="E124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -6620,7 +6620,7 @@
         <v>2020</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="E125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -6638,7 +6638,7 @@
         <v>2020</v>
       </c>
       <c r="B126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="E126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -6656,7 +6656,7 @@
         <v>2020</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127">
         <v>10</v>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="E127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -6674,7 +6674,7 @@
         <v>2020</v>
       </c>
       <c r="B128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128">
         <v>10</v>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="E128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -6692,7 +6692,7 @@
         <v>2020</v>
       </c>
       <c r="B129">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C129">
         <v>10</v>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -6710,7 +6710,7 @@
         <v>2020</v>
       </c>
       <c r="B130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C130">
         <v>10</v>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="E130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -6728,7 +6728,7 @@
         <v>2020</v>
       </c>
       <c r="B131">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C131">
         <v>10</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="E131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6746,7 +6746,7 @@
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C132">
         <v>10</v>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -6764,7 +6764,7 @@
         <v>2020</v>
       </c>
       <c r="B133">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C133">
         <v>10</v>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="E133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6782,7 +6782,7 @@
         <v>2020</v>
       </c>
       <c r="B134">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C134">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6800,7 +6800,7 @@
         <v>2020</v>
       </c>
       <c r="B135">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C135">
         <v>10</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="E135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -6818,7 +6818,7 @@
         <v>2020</v>
       </c>
       <c r="B136">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C136">
         <v>10</v>
@@ -6828,6 +6828,24 @@
       </c>
       <c r="E136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>2020</v>
+      </c>
+      <c r="B137">
+        <v>14</v>
+      </c>
+      <c r="C137">
+        <v>10</v>
+      </c>
+      <c r="D137">
+        <v>-1</v>
+      </c>
+      <c r="E137" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
         <v>クリーパー</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -683,10 +683,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -724,16 +724,30 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -747,8 +761,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -771,83 +845,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -862,7 +862,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,13 +994,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,91 +1006,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -988,43 +1024,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1042,7 +1042,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,15 +1053,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1076,6 +1067,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1097,10 +1112,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1108,24 +1130,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1144,15 +1153,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1161,7 +1161,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1170,136 +1170,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3776,7 +3776,7 @@
         <v>3</v>
       </c>
       <c r="G29">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -4381,7 +4381,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.45454545454546" customWidth="1"/>
@@ -6278,17 +6278,17 @@
         <v>1030</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D106">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -6296,17 +6296,17 @@
         <v>1030</v>
       </c>
       <c r="B107">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D107">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -6314,71 +6314,71 @@
         <v>1030</v>
       </c>
       <c r="B108">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C108">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D108">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C109">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D109">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B110">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C110">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D110">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B111">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C111">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D111">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -6386,7 +6386,7 @@
         <v>1040</v>
       </c>
       <c r="B112">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="E112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -6404,7 +6404,7 @@
         <v>1040</v>
       </c>
       <c r="B113">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C113">
         <v>15</v>
@@ -6414,15 +6414,15 @@
       </c>
       <c r="E113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C114">
         <v>15</v>
@@ -6432,15 +6432,15 @@
       </c>
       <c r="E114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B115">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C115">
         <v>15</v>
@@ -6450,15 +6450,15 @@
       </c>
       <c r="E115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B116">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C116">
         <v>15</v>
@@ -6468,61 +6468,61 @@
       </c>
       <c r="E116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C117">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D117">
         <v>-1</v>
       </c>
       <c r="E117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C118">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D118">
         <v>-1</v>
       </c>
       <c r="E118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B119">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C119">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D119">
         <v>-1</v>
       </c>
       <c r="E119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -6530,7 +6530,7 @@
         <v>2010</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C120">
         <v>10</v>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -6548,7 +6548,7 @@
         <v>2010</v>
       </c>
       <c r="B121">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C121">
         <v>10</v>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="E121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -6566,7 +6566,7 @@
         <v>2010</v>
       </c>
       <c r="B122">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C122">
         <v>10</v>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -6584,7 +6584,7 @@
         <v>2010</v>
       </c>
       <c r="B123">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C123">
         <v>10</v>
@@ -6594,15 +6594,15 @@
       </c>
       <c r="E123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C124">
         <v>10</v>
@@ -6612,15 +6612,15 @@
       </c>
       <c r="E124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -6630,15 +6630,15 @@
       </c>
       <c r="E125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="E126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -6656,7 +6656,7 @@
         <v>2020</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C127">
         <v>10</v>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="E127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -6674,7 +6674,7 @@
         <v>2020</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>10</v>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="E128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -6692,7 +6692,7 @@
         <v>2020</v>
       </c>
       <c r="B129">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C129">
         <v>10</v>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="E129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -6710,7 +6710,7 @@
         <v>2020</v>
       </c>
       <c r="B130">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C130">
         <v>10</v>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="E130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -6728,7 +6728,7 @@
         <v>2020</v>
       </c>
       <c r="B131">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C131">
         <v>10</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="E131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6746,7 +6746,7 @@
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C132">
         <v>10</v>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -6764,7 +6764,7 @@
         <v>2020</v>
       </c>
       <c r="B133">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C133">
         <v>10</v>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="E133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6782,7 +6782,7 @@
         <v>2020</v>
       </c>
       <c r="B134">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C134">
         <v>10</v>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6800,7 +6800,7 @@
         <v>2020</v>
       </c>
       <c r="B135">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C135">
         <v>10</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="E135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -6818,7 +6818,7 @@
         <v>2020</v>
       </c>
       <c r="B136">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C136">
         <v>10</v>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="E136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -6836,7 +6836,7 @@
         <v>2020</v>
       </c>
       <c r="B137">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C137">
         <v>10</v>
@@ -6846,6 +6846,60 @@
       </c>
       <c r="E137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
+        <v>スクイッド</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>2020</v>
+      </c>
+      <c r="B138">
+        <v>12</v>
+      </c>
+      <c r="C138">
+        <v>10</v>
+      </c>
+      <c r="D138">
+        <v>-1</v>
+      </c>
+      <c r="E138" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>2020</v>
+      </c>
+      <c r="B139">
+        <v>13</v>
+      </c>
+      <c r="C139">
+        <v>10</v>
+      </c>
+      <c r="D139">
+        <v>-1</v>
+      </c>
+      <c r="E139" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>2020</v>
+      </c>
+      <c r="B140">
+        <v>14</v>
+      </c>
+      <c r="C140">
+        <v>10</v>
+      </c>
+      <c r="D140">
+        <v>-1</v>
+      </c>
+      <c r="E140" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
         <v>クリーパー</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="207">
   <si>
     <t>Id</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>Paved</t>
-  </si>
-  <si>
-    <t>DarkStorm</t>
   </si>
   <si>
     <t>040-Tower02</t>
@@ -683,10 +680,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -710,29 +707,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -747,7 +722,82 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -761,68 +811,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -837,9 +835,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -847,7 +844,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -862,7 +859,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,19 +985,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,55 +1009,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -958,61 +1021,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,24 +1043,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1053,30 +1050,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1110,11 +1083,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1130,11 +1109,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1153,6 +1130,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1161,25 +1158,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1188,118 +1185,118 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3021,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -3136,7 +3133,7 @@
         <v>2040</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -3260,7 +3257,7 @@
         <v>2040</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R20" t="s">
         <v>26</v>
@@ -3322,7 +3319,7 @@
         <v>2040</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R21" t="s">
         <v>26</v>
@@ -3384,7 +3381,7 @@
         <v>2040</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R22" t="s">
         <v>26</v>
@@ -3393,7 +3390,7 @@
         <v>5010</v>
       </c>
       <c r="T22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -3446,13 +3443,13 @@
         <v>2040</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
       </c>
       <c r="T23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -3505,13 +3502,13 @@
         <v>2040</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R24" t="s">
         <v>26</v>
       </c>
       <c r="T24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -3564,13 +3561,13 @@
         <v>2040</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R25" t="s">
         <v>26</v>
       </c>
       <c r="T25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -3623,13 +3620,13 @@
         <v>2040</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R26" t="s">
         <v>26</v>
       </c>
       <c r="T26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -3930,7 +3927,7 @@
         <v>2040</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R31" t="s">
         <v>24</v>
@@ -3992,7 +3989,7 @@
         <v>2020</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R32" t="s">
         <v>24</v>
@@ -4001,7 +3998,7 @@
         <v>20010</v>
       </c>
       <c r="T32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -4054,7 +4051,7 @@
         <v>2020</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R33" t="s">
         <v>24</v>
@@ -4063,7 +4060,7 @@
         <v>20020</v>
       </c>
       <c r="T33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -4116,7 +4113,7 @@
         <v>3020</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R34" t="s">
         <v>24</v>
@@ -4125,7 +4122,7 @@
         <v>20030</v>
       </c>
       <c r="T34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -4178,7 +4175,7 @@
         <v>1060</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R35" t="s">
         <v>21</v>
@@ -4187,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -4240,7 +4237,7 @@
         <v>1060</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R36" t="s">
         <v>21</v>
@@ -4249,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4273,34 +4270,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>44</v>
-      </c>
-      <c r="K1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4392,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>47</v>
-      </c>
-      <c r="D1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5111,7 +5108,7 @@
         <v>3</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>-1</v>
@@ -5129,7 +5126,7 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>-1</v>
@@ -5147,7 +5144,7 @@
         <v>6</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>-1</v>
@@ -5165,7 +5162,7 @@
         <v>8</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>-1</v>
@@ -5183,7 +5180,7 @@
         <v>11</v>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>-1</v>
@@ -6920,25 +6917,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>53</v>
-      </c>
-      <c r="H1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6992,16 +6989,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7009,13 +7006,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>21</v>
@@ -7026,13 +7023,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -7043,16 +7040,16 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7060,13 +7057,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -7077,16 +7074,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -7094,13 +7091,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -7111,13 +7108,13 @@
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -7128,13 +7125,13 @@
         <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -7145,16 +7142,16 @@
         <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7162,13 +7159,13 @@
         <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
@@ -7179,13 +7176,13 @@
         <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -7196,16 +7193,16 @@
         <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7213,13 +7210,13 @@
         <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
@@ -7230,13 +7227,13 @@
         <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
@@ -7247,13 +7244,13 @@
         <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -7264,13 +7261,13 @@
         <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
@@ -7281,16 +7278,16 @@
         <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7298,13 +7295,13 @@
         <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
@@ -7315,13 +7312,13 @@
         <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -7332,13 +7329,13 @@
         <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -7349,13 +7346,13 @@
         <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
@@ -7366,16 +7363,16 @@
         <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7383,13 +7380,13 @@
         <v>71</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -7400,13 +7397,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -7417,13 +7414,13 @@
         <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -7434,13 +7431,13 @@
         <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
@@ -7451,16 +7448,16 @@
         <v>1010</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="29" ht="25" spans="1:7">
@@ -7468,16 +7465,16 @@
         <v>1020</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="F29" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="30" ht="25" spans="1:7">
@@ -7485,16 +7482,16 @@
         <v>1030</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="F30" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="31" ht="25" spans="1:7">
@@ -7502,16 +7499,16 @@
         <v>1040</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="F31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="32" ht="25" spans="1:7">
@@ -7519,16 +7516,16 @@
         <v>1050</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G32" s="4" t="s">
         <v>132</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="33" ht="37.5" spans="1:7">
@@ -7536,16 +7533,16 @@
         <v>2010</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="F33" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="34" ht="37.5" spans="1:7">
@@ -7553,16 +7550,16 @@
         <v>2020</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="G34" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" ht="37.5" spans="1:7">
@@ -7570,16 +7567,16 @@
         <v>2030</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="G35" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="3:4">
@@ -7611,19 +7608,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7631,31 +7628,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2">
+        <v>-1</v>
+      </c>
+      <c r="J2" t="s">
         <v>145</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="K2">
+        <v>-1</v>
+      </c>
+      <c r="L2" t="s">
         <v>145</v>
       </c>
-      <c r="I2">
-        <v>-1</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="K2">
-        <v>-1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -7663,34 +7660,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -7698,34 +7695,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D4">
         <v>1020</v>
       </c>
       <c r="E4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
         <v>154</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>155</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -7733,34 +7730,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D5">
         <v>1030</v>
       </c>
       <c r="E5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -7768,34 +7765,34 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D6">
         <v>2010</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -7803,34 +7800,34 @@
         <v>3010</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D7">
         <v>2011</v>
       </c>
       <c r="E7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -7838,28 +7835,28 @@
         <v>2020</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -7867,28 +7864,28 @@
         <v>2021</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -7896,28 +7893,28 @@
         <v>2030</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -7925,19 +7922,19 @@
         <v>3010</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -7945,19 +7942,19 @@
         <v>3020</v>
       </c>
       <c r="E12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -7965,19 +7962,19 @@
         <v>3030</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -7985,13 +7982,13 @@
         <v>4010</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -7999,7 +7996,7 @@
         <v>4011</v>
       </c>
       <c r="E15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -8007,7 +8004,7 @@
         <v>4020</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -8015,7 +8012,7 @@
         <v>5010</v>
       </c>
       <c r="E17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -8023,7 +8020,7 @@
         <v>5020</v>
       </c>
       <c r="E18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -8031,7 +8028,7 @@
         <v>6010</v>
       </c>
       <c r="E19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -8039,7 +8036,7 @@
         <v>6011</v>
       </c>
       <c r="E20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -8047,7 +8044,7 @@
         <v>6020</v>
       </c>
       <c r="E21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -8055,7 +8052,7 @@
         <v>6030</v>
       </c>
       <c r="E22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -8063,7 +8060,7 @@
         <v>7010</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -8071,7 +8068,7 @@
         <v>7020</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -8079,7 +8076,7 @@
         <v>7021</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -8087,7 +8084,7 @@
         <v>8010</v>
       </c>
       <c r="E26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -8095,7 +8092,7 @@
         <v>9010</v>
       </c>
       <c r="E27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -302,12 +302,6 @@
 Without a doubt, soul-consuming creatures dwell within.</t>
   </si>
   <si>
-    <t>暗黒の塔・1F</t>
-  </si>
-  <si>
-    <t>Dark Tower - 1F</t>
-  </si>
-  <si>
     <t>暗黒の塔・2F</t>
   </si>
   <si>
@@ -324,6 +318,12 @@
   </si>
   <si>
     <t>Dark Tower - 4F</t>
+  </si>
+  <si>
+    <t>暗黒の塔・屋上</t>
+  </si>
+  <si>
+    <t>Dark Tower - Roof Top</t>
   </si>
   <si>
     <t>天空城</t>
@@ -681,9 +681,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -706,23 +706,54 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -736,23 +767,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -767,53 +783,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -836,6 +807,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -843,10 +843,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -859,7 +859,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,19 +919,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,19 +937,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -919,13 +967,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -943,13 +1009,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -961,37 +1021,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1003,43 +1033,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,17 +1053,32 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1084,49 +1099,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1142,10 +1135,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1158,145 +1158,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802" activeTab="4"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -707,40 +707,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -753,22 +723,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -784,30 +753,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -820,15 +788,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -849,6 +810,45 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -859,7 +859,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,7 +937,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,43 +949,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -931,19 +979,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -955,55 +1003,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1015,25 +1033,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1053,21 +1053,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1079,6 +1064,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1115,11 +1109,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1135,18 +1127,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1158,145 +1158,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2743,10 +2743,10 @@
         <v>30</v>
       </c>
       <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="L12">
         <v>8</v>
-      </c>
-      <c r="L12">
-        <v>12</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -2805,10 +2805,10 @@
         <v>30</v>
       </c>
       <c r="K13">
+        <v>5</v>
+      </c>
+      <c r="L13">
         <v>8</v>
-      </c>
-      <c r="L13">
-        <v>12</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -2867,10 +2867,10 @@
         <v>30</v>
       </c>
       <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="L14">
         <v>8</v>
-      </c>
-      <c r="L14">
-        <v>12</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -2929,10 +2929,10 @@
         <v>30</v>
       </c>
       <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
         <v>8</v>
-      </c>
-      <c r="L15">
-        <v>12</v>
       </c>
       <c r="M15">
         <v>-1</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -8,24 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
-    <sheet name="StageEvents" sheetId="2" r:id="rId2"/>
-    <sheet name="StageEnemyRates" sheetId="9" r:id="rId3"/>
-    <sheet name="Tutorials" sheetId="4" r:id="rId4"/>
-    <sheet name="TextData" sheetId="5" r:id="rId5"/>
-    <sheet name="Define" sheetId="6" r:id="rId6"/>
+    <sheet name="StageEnemyRates" sheetId="9" r:id="rId2"/>
+    <sheet name="TextData" sheetId="5" r:id="rId3"/>
+    <sheet name="Define" sheetId="6" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">StageEvents!$F$1:$F$21</definedName>
-  </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="194">
   <si>
     <t>Id</t>
   </si>
@@ -135,33 +130,6 @@
     <t>CloudedSunGlow</t>
   </si>
   <si>
-    <t>PositionX</t>
-  </si>
-  <si>
-    <t>PositionY</t>
-  </si>
-  <si>
-    <t>Timing</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Param</t>
-  </si>
-  <si>
-    <t>Param2</t>
-  </si>
-  <si>
-    <t>Param3</t>
-  </si>
-  <si>
-    <t>ReadFlag</t>
-  </si>
-  <si>
     <t>EnemyId</t>
   </si>
   <si>
@@ -169,24 +137,6 @@
   </si>
   <si>
     <t>LineIndex</t>
-  </si>
-  <si>
-    <t>Turns</t>
-  </si>
-  <si>
-    <t>SceneType</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>Height</t>
   </si>
   <si>
     <t>Text</t>
@@ -472,6 +422,12 @@
   </si>
   <si>
     <t>Ragnarok - Battlefield</t>
+  </si>
+  <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
   <si>
     <t>SymbolType</t>
@@ -681,9 +637,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -714,30 +670,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -748,51 +698,6 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -812,7 +717,74 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -821,22 +793,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -865,7 +821,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,25 +857,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -913,7 +881,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -925,7 +917,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,31 +941,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -973,13 +971,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -991,55 +989,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1050,6 +1006,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1072,7 +1037,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1092,6 +1066,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1103,35 +1088,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1158,145 +1114,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2855,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -2917,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -2979,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
@@ -3841,7 +3797,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>30</v>
@@ -3862,7 +3818,7 @@
         <v>3010</v>
       </c>
       <c r="P30">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="Q30" s="1" t="s">
         <v>30</v>
@@ -4258,127 +4214,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="2"/>
-  <cols>
-    <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="21.7272727272727" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>2010</v>
-      </c>
-      <c r="F2">
-        <v>1010</v>
-      </c>
-      <c r="G2" t="str">
-        <f>INDEX(Define!E:E,MATCH(F2,Define!D:D))</f>
-        <v>Adv再生</v>
-      </c>
-      <c r="H2">
-        <v>30110</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2010</v>
-      </c>
-      <c r="F3">
-        <v>9010</v>
-      </c>
-      <c r="G3" t="str">
-        <f>INDEX(Define!E:E,MATCH(F3,Define!D:D))</f>
-        <v>イベント終了明示</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="F1:F21">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.45454545454546" customWidth="1"/>
@@ -4389,13 +4225,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5105,7 +4941,7 @@
         <v>50</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -5115,7 +4951,7 @@
       </c>
       <c r="E41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B41,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5123,7 +4959,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C42">
         <v>7</v>
@@ -5133,7 +4969,7 @@
       </c>
       <c r="E42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B42,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -5177,17 +5013,17 @@
         <v>50</v>
       </c>
       <c r="B45">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C45">
         <v>7</v>
       </c>
       <c r="D45">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B45,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -5195,17 +5031,17 @@
         <v>51</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>-1</v>
       </c>
       <c r="E46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B46,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -5213,17 +5049,17 @@
         <v>51</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>-1</v>
       </c>
       <c r="E47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B47,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5234,7 +5070,7 @@
         <v>6</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>-1</v>
@@ -5252,7 +5088,7 @@
         <v>8</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>-1</v>
@@ -5267,17 +5103,17 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D50">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B50,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -5285,17 +5121,17 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>-1</v>
       </c>
       <c r="E51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B51,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -5303,17 +5139,17 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>-1</v>
       </c>
       <c r="E52" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B52,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5324,7 +5160,7 @@
         <v>6</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>-1</v>
@@ -5342,7 +5178,7 @@
         <v>8</v>
       </c>
       <c r="C54">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>-1</v>
@@ -5357,17 +5193,17 @@
         <v>52</v>
       </c>
       <c r="B55">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C55">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D55">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B55,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -5375,17 +5211,17 @@
         <v>53</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>-1</v>
       </c>
       <c r="E56" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B56,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -5393,17 +5229,17 @@
         <v>53</v>
       </c>
       <c r="B57">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>-1</v>
       </c>
       <c r="E57" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B57,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -5414,7 +5250,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>-1</v>
@@ -5432,7 +5268,7 @@
         <v>8</v>
       </c>
       <c r="C59">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>-1</v>
@@ -5447,17 +5283,17 @@
         <v>53</v>
       </c>
       <c r="B60">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C60">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D60">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B60,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -6383,17 +6219,17 @@
         <v>1040</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D112">
         <v>-1</v>
       </c>
       <c r="E112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -6401,17 +6237,17 @@
         <v>1040</v>
       </c>
       <c r="B113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D113">
         <v>-1</v>
       </c>
       <c r="E113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -6422,7 +6258,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D114">
         <v>-1</v>
@@ -6440,7 +6276,7 @@
         <v>8</v>
       </c>
       <c r="C115">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D115">
         <v>-1</v>
@@ -6455,17 +6291,17 @@
         <v>1040</v>
       </c>
       <c r="B116">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C116">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D116">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -6656,10 +6492,10 @@
         <v>1</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D127">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
@@ -6674,10 +6510,10 @@
         <v>2</v>
       </c>
       <c r="C128">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D128">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
@@ -6689,17 +6525,17 @@
         <v>2020</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C129">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D129">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -6707,17 +6543,17 @@
         <v>2020</v>
       </c>
       <c r="B130">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D130">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -6725,17 +6561,17 @@
         <v>2020</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D131">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6743,17 +6579,17 @@
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C132">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D132">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -6761,17 +6597,17 @@
         <v>2020</v>
       </c>
       <c r="B133">
+        <v>12</v>
+      </c>
+      <c r="C133">
         <v>7</v>
       </c>
-      <c r="C133">
-        <v>10</v>
-      </c>
       <c r="D133">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6779,17 +6615,17 @@
         <v>2020</v>
       </c>
       <c r="B134">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C134">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D134">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6797,106 +6633,16 @@
         <v>2020</v>
       </c>
       <c r="B135">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C135">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D135">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136">
-        <v>2020</v>
-      </c>
-      <c r="B136">
-        <v>10</v>
-      </c>
-      <c r="C136">
-        <v>10</v>
-      </c>
-      <c r="D136">
-        <v>-1</v>
-      </c>
-      <c r="E136" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137">
-        <v>2020</v>
-      </c>
-      <c r="B137">
-        <v>11</v>
-      </c>
-      <c r="C137">
-        <v>10</v>
-      </c>
-      <c r="D137">
-        <v>-1</v>
-      </c>
-      <c r="E137" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138">
-        <v>2020</v>
-      </c>
-      <c r="B138">
-        <v>12</v>
-      </c>
-      <c r="C138">
-        <v>10</v>
-      </c>
-      <c r="D138">
-        <v>-1</v>
-      </c>
-      <c r="E138" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139">
-        <v>2020</v>
-      </c>
-      <c r="B139">
-        <v>13</v>
-      </c>
-      <c r="C139">
-        <v>10</v>
-      </c>
-      <c r="D139">
-        <v>-1</v>
-      </c>
-      <c r="E139" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>インプ</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
-      <c r="A140">
-        <v>2020</v>
-      </c>
-      <c r="B140">
-        <v>14</v>
-      </c>
-      <c r="C140">
-        <v>10</v>
-      </c>
-      <c r="D140">
-        <v>-1</v>
-      </c>
-      <c r="E140" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
         <v>クリーパー</v>
       </c>
     </row>
@@ -6906,71 +6652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="1" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2">
-        <v>1010</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>110</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G38"/>
@@ -6989,16 +6671,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7006,13 +6688,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>21</v>
@@ -7023,13 +6705,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -7040,16 +6722,16 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7057,13 +6739,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -7074,16 +6756,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -7091,13 +6773,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -7108,13 +6790,13 @@
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -7125,13 +6807,13 @@
         <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
@@ -7142,16 +6824,16 @@
         <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7159,13 +6841,13 @@
         <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
@@ -7176,13 +6858,13 @@
         <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -7193,16 +6875,16 @@
         <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7210,13 +6892,13 @@
         <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>21</v>
@@ -7227,13 +6909,13 @@
         <v>52</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
@@ -7244,13 +6926,13 @@
         <v>53</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -7261,13 +6943,13 @@
         <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
@@ -7278,16 +6960,16 @@
         <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7295,13 +6977,13 @@
         <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
@@ -7312,13 +6994,13 @@
         <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -7329,13 +7011,13 @@
         <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -7346,13 +7028,13 @@
         <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>21</v>
@@ -7363,16 +7045,16 @@
         <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7380,13 +7062,13 @@
         <v>71</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -7397,13 +7079,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -7414,13 +7096,13 @@
         <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -7431,13 +7113,13 @@
         <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
@@ -7448,16 +7130,16 @@
         <v>1010</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" ht="25" spans="1:7">
@@ -7465,16 +7147,16 @@
         <v>1020</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" ht="25" spans="1:7">
@@ -7482,16 +7164,16 @@
         <v>1030</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" ht="25" spans="1:7">
@@ -7499,16 +7181,16 @@
         <v>1040</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="25" spans="1:7">
@@ -7516,16 +7198,16 @@
         <v>1050</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" ht="37.5" spans="1:7">
@@ -7533,16 +7215,16 @@
         <v>2010</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" ht="37.5" spans="1:7">
@@ -7550,16 +7232,16 @@
         <v>2020</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" ht="37.5" spans="1:7">
@@ -7567,16 +7249,16 @@
         <v>2030</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="3:4">
@@ -7595,7 +7277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O28"/>
@@ -7608,19 +7290,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="I1" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7628,31 +7310,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -7660,34 +7342,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -7695,34 +7377,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="D4">
         <v>1020</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -7730,34 +7412,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D5">
         <v>1030</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -7765,34 +7447,34 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D6">
         <v>2010</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -7800,34 +7482,34 @@
         <v>3010</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D7">
         <v>2011</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -7835,28 +7517,28 @@
         <v>2020</v>
       </c>
       <c r="E8" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -7864,28 +7546,28 @@
         <v>2021</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -7893,28 +7575,28 @@
         <v>2030</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -7922,19 +7604,19 @@
         <v>3010</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -7942,19 +7624,19 @@
         <v>3020</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -7962,19 +7644,19 @@
         <v>3030</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -7982,13 +7664,13 @@
         <v>4010</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -7996,7 +7678,7 @@
         <v>4011</v>
       </c>
       <c r="E15" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -8004,7 +7686,7 @@
         <v>4020</v>
       </c>
       <c r="E16" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -8012,7 +7694,7 @@
         <v>5010</v>
       </c>
       <c r="E17" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -8020,7 +7702,7 @@
         <v>5020</v>
       </c>
       <c r="E18" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -8028,7 +7710,7 @@
         <v>6010</v>
       </c>
       <c r="E19" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -8036,7 +7718,7 @@
         <v>6011</v>
       </c>
       <c r="E20" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -8044,7 +7726,7 @@
         <v>6020</v>
       </c>
       <c r="E21" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -8052,7 +7734,7 @@
         <v>6030</v>
       </c>
       <c r="E22" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -8060,7 +7742,7 @@
         <v>7010</v>
       </c>
       <c r="E23" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -8068,7 +7750,7 @@
         <v>7020</v>
       </c>
       <c r="E24" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -8076,7 +7758,7 @@
         <v>7021</v>
       </c>
       <c r="E25" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -8084,7 +7766,7 @@
         <v>8010</v>
       </c>
       <c r="E26" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -8092,7 +7774,7 @@
         <v>9010</v>
       </c>
       <c r="E27" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="196">
   <si>
     <t>Id</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>Dark Tower - 4F</t>
+  </si>
+  <si>
+    <t>暗黒の塔・5F</t>
+  </si>
+  <si>
+    <t>Dark Tower - 5F</t>
   </si>
   <si>
     <t>暗黒の塔・屋上</t>
@@ -636,10 +642,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -662,32 +668,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -698,21 +681,6 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -737,6 +705,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -744,8 +720,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -759,40 +782,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -821,7 +827,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,19 +905,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,115 +929,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -989,13 +953,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1006,15 +1012,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1037,16 +1034,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1068,11 +1067,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1088,6 +1085,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1114,145 +1120,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1973,7 +1979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="5" max="6" width="10.3636363636364" customWidth="1"/>
@@ -2699,10 +2705,10 @@
         <v>30</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -2761,10 +2767,10 @@
         <v>30</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -2823,10 +2829,10 @@
         <v>30</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -2885,10 +2891,10 @@
         <v>30</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -2947,10 +2953,10 @@
         <v>30</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2974,36 +2980,36 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B17">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>30</v>
@@ -3018,22 +3024,22 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="O17">
         <v>3010</v>
       </c>
       <c r="P17">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R17" t="s">
         <v>26</v>
       </c>
       <c r="S17">
-        <v>5010</v>
+        <v>0</v>
       </c>
       <c r="T17" t="s">
         <v>22</v>
@@ -3041,10 +3047,10 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -3053,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -3065,16 +3071,16 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>30</v>
       </c>
       <c r="K18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -3089,13 +3095,13 @@
         <v>2040</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>5010</v>
       </c>
       <c r="T18" t="s">
         <v>22</v>
@@ -3103,10 +3109,10 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -3151,7 +3157,7 @@
         <v>2040</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -3165,10 +3171,10 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -3213,7 +3219,7 @@
         <v>2040</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R20" t="s">
         <v>26</v>
@@ -3227,10 +3233,10 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -3257,10 +3263,10 @@
         <v>30</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -3284,51 +3290,51 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:20">
       <c r="A22">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B22">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>30</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="O22">
         <v>3010</v>
@@ -3337,24 +3343,24 @@
         <v>2040</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R22" t="s">
         <v>26</v>
       </c>
       <c r="S22">
-        <v>5010</v>
+        <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -3363,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -3404,16 +3410,19 @@
       <c r="R23" t="s">
         <v>26</v>
       </c>
+      <c r="S23">
+        <v>5010</v>
+      </c>
       <c r="T23" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:20">
       <c r="A24">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B24">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24">
         <v>7</v>
@@ -3469,10 +3478,10 @@
     </row>
     <row r="25" spans="1:20">
       <c r="A25">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -3528,10 +3537,10 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -3558,10 +3567,10 @@
         <v>30</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -3570,7 +3579,7 @@
         <v>1060</v>
       </c>
       <c r="O26">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="P26">
         <v>2040</v>
@@ -3587,75 +3596,72 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27">
-        <v>1010</v>
+        <v>74</v>
       </c>
       <c r="B27">
-        <v>1010</v>
+        <v>74</v>
       </c>
       <c r="C27">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>30</v>
       </c>
       <c r="K27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="N27">
-        <v>1210</v>
+        <v>1060</v>
       </c>
       <c r="O27">
-        <v>3010</v>
+        <v>3030</v>
       </c>
       <c r="P27">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R27" t="s">
-        <v>24</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T27" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="A28">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B28">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="C28">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28">
         <v>11</v>
@@ -3664,16 +3670,16 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28">
         <v>30</v>
@@ -3697,7 +3703,7 @@
         <v>2010</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R28" t="s">
         <v>24</v>
@@ -3711,13 +3717,13 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B29">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="C29">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D29">
         <v>11</v>
@@ -3726,16 +3732,16 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>30</v>
@@ -3756,10 +3762,10 @@
         <v>3010</v>
       </c>
       <c r="P29">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R29" t="s">
         <v>24</v>
@@ -3768,18 +3774,18 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B30">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="C30">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D30">
         <v>11</v>
@@ -3788,16 +3794,16 @@
         <v>1</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J30">
         <v>30</v>
@@ -3821,7 +3827,7 @@
         <v>2030</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R30" t="s">
         <v>24</v>
@@ -3830,18 +3836,18 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B31">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="C31">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D31">
         <v>11</v>
@@ -3850,16 +3856,16 @@
         <v>1</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>30</v>
@@ -3880,10 +3886,10 @@
         <v>3010</v>
       </c>
       <c r="P31">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R31" t="s">
         <v>24</v>
@@ -3897,75 +3903,75 @@
     </row>
     <row r="32" spans="1:20">
       <c r="A32">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B32">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="C32">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>30</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>2020</v>
+        <v>1210</v>
       </c>
       <c r="O32">
         <v>3010</v>
       </c>
       <c r="P32">
-        <v>2020</v>
+        <v>2040</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="R32" t="s">
         <v>24</v>
       </c>
       <c r="S32">
-        <v>20010</v>
+        <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B33">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="C33">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -3974,10 +3980,10 @@
         <v>1</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -4013,7 +4019,7 @@
         <v>24</v>
       </c>
       <c r="S33">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="T33" t="s">
         <v>35</v>
@@ -4021,13 +4027,13 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B34">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C34">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -4036,10 +4042,10 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -4060,13 +4066,13 @@
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="O34">
         <v>3010</v>
       </c>
       <c r="P34">
-        <v>3020</v>
+        <v>2020</v>
       </c>
       <c r="Q34" s="1" t="s">
         <v>34</v>
@@ -4075,7 +4081,7 @@
         <v>24</v>
       </c>
       <c r="S34">
-        <v>20030</v>
+        <v>20020</v>
       </c>
       <c r="T34" t="s">
         <v>35</v>
@@ -4083,31 +4089,31 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B35">
-        <v>73</v>
+        <v>2030</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>30</v>
@@ -4122,33 +4128,33 @@
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>1060</v>
+        <v>3020</v>
       </c>
       <c r="O35">
         <v>3010</v>
       </c>
       <c r="P35">
-        <v>1060</v>
+        <v>3020</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R35" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>20030</v>
       </c>
       <c r="T35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B36">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -4202,6 +4208,68 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37">
+        <v>3011</v>
+      </c>
+      <c r="B37">
+        <v>74</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>30</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>-1</v>
+      </c>
+      <c r="N37">
+        <v>1060</v>
+      </c>
+      <c r="O37">
+        <v>3010</v>
+      </c>
+      <c r="P37">
+        <v>1060</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" t="s">
+        <v>21</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4214,7 +4282,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.45454545454546" customWidth="1"/>
@@ -5298,88 +5366,88 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>-1</v>
       </c>
       <c r="E61" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B61,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B62">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>-1</v>
       </c>
       <c r="E62" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B62,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B63">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>-1</v>
       </c>
       <c r="E63" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B63,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B64">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>-1</v>
       </c>
       <c r="E64" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B64,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B65">
         <v>13</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D65">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B65,[1]TextData!A:A))</f>
@@ -5388,10 +5456,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B66">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C66">
         <v>10</v>
@@ -5401,15 +5469,15 @@
       </c>
       <c r="E66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B66,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C67">
         <v>10</v>
@@ -5419,15 +5487,15 @@
       </c>
       <c r="E67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B67,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B68">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68">
         <v>10</v>
@@ -5437,15 +5505,15 @@
       </c>
       <c r="E68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B68,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C69">
         <v>10</v>
@@ -5455,15 +5523,15 @@
       </c>
       <c r="E69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B69,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C70">
         <v>10</v>
@@ -5473,15 +5541,15 @@
       </c>
       <c r="E70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B70,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C71">
         <v>10</v>
@@ -5491,15 +5559,15 @@
       </c>
       <c r="E71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B71,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B72">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C72">
         <v>10</v>
@@ -5509,15 +5577,15 @@
       </c>
       <c r="E72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B72,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B73">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73">
         <v>10</v>
@@ -5527,15 +5595,15 @@
       </c>
       <c r="E73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B73,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B74">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -5545,7 +5613,7 @@
       </c>
       <c r="E74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B74,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -5553,7 +5621,7 @@
         <v>70</v>
       </c>
       <c r="B75">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C75">
         <v>10</v>
@@ -5563,7 +5631,7 @@
       </c>
       <c r="E75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B75,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -5571,7 +5639,7 @@
         <v>70</v>
       </c>
       <c r="B76">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>10</v>
@@ -5581,15 +5649,15 @@
       </c>
       <c r="E76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B76,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -5599,15 +5667,15 @@
       </c>
       <c r="E77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B77,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C78">
         <v>10</v>
@@ -5617,15 +5685,15 @@
       </c>
       <c r="E78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C79">
         <v>10</v>
@@ -5635,15 +5703,15 @@
       </c>
       <c r="E79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B80">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C80">
         <v>10</v>
@@ -5653,15 +5721,15 @@
       </c>
       <c r="E80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B81">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C81">
         <v>10</v>
@@ -5671,7 +5739,7 @@
       </c>
       <c r="E81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -5679,7 +5747,7 @@
         <v>71</v>
       </c>
       <c r="B82">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>10</v>
@@ -5689,7 +5757,7 @@
       </c>
       <c r="E82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -5697,7 +5765,7 @@
         <v>71</v>
       </c>
       <c r="B83">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C83">
         <v>10</v>
@@ -5707,15 +5775,15 @@
       </c>
       <c r="E83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C84">
         <v>10</v>
@@ -5725,15 +5793,15 @@
       </c>
       <c r="E84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C85">
         <v>10</v>
@@ -5743,15 +5811,15 @@
       </c>
       <c r="E85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C86">
         <v>10</v>
@@ -5761,15 +5829,15 @@
       </c>
       <c r="E86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B87">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C87">
         <v>10</v>
@@ -5779,15 +5847,15 @@
       </c>
       <c r="E87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B88">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88">
         <v>10</v>
@@ -5797,7 +5865,7 @@
       </c>
       <c r="E88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -5805,7 +5873,7 @@
         <v>72</v>
       </c>
       <c r="B89">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C89">
         <v>10</v>
@@ -5815,15 +5883,15 @@
       </c>
       <c r="E89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C90">
         <v>10</v>
@@ -5833,15 +5901,15 @@
       </c>
       <c r="E90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C91">
         <v>10</v>
@@ -5851,15 +5919,15 @@
       </c>
       <c r="E91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B92">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C92">
         <v>10</v>
@@ -5869,15 +5937,15 @@
       </c>
       <c r="E92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B93">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C93">
         <v>10</v>
@@ -5887,15 +5955,15 @@
       </c>
       <c r="E93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B94">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C94">
         <v>10</v>
@@ -5905,7 +5973,7 @@
       </c>
       <c r="E94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -5913,7 +5981,7 @@
         <v>73</v>
       </c>
       <c r="B95">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>10</v>
@@ -5923,7 +5991,7 @@
       </c>
       <c r="E95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -5931,7 +5999,7 @@
         <v>73</v>
       </c>
       <c r="B96">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C96">
         <v>10</v>
@@ -5941,102 +6009,102 @@
       </c>
       <c r="E96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D97">
         <v>-1</v>
       </c>
       <c r="E97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B98">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C98">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D98">
         <v>-1</v>
       </c>
       <c r="E98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B99">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C99">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D99">
         <v>-1</v>
       </c>
       <c r="E99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>1010</v>
+        <v>73</v>
       </c>
       <c r="B100">
+        <v>11</v>
+      </c>
+      <c r="C100">
         <v>10</v>
-      </c>
-      <c r="C100">
-        <v>15</v>
       </c>
       <c r="D100">
         <v>-1</v>
       </c>
       <c r="E100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>1020</v>
+        <v>73</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C101">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D101">
         <v>-1</v>
       </c>
       <c r="E101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B102">
         <v>3</v>
@@ -6054,7 +6122,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -6072,10 +6140,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C104">
         <v>15</v>
@@ -6085,15 +6153,15 @@
       </c>
       <c r="E104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B105">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C105">
         <v>15</v>
@@ -6103,21 +6171,21 @@
       </c>
       <c r="E105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
@@ -6126,34 +6194,34 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C107">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B108">
         <v>4</v>
       </c>
       <c r="C108">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
@@ -6162,38 +6230,38 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B109">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C109">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B110">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C110">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -6201,251 +6269,251 @@
         <v>1030</v>
       </c>
       <c r="B111">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C111">
         <v>10</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D112">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D113">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B114">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D114">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B115">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D115">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B116">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D116">
         <v>2</v>
       </c>
       <c r="E116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B117">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D117">
         <v>-1</v>
       </c>
       <c r="E117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B118">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D118">
         <v>-1</v>
       </c>
       <c r="E118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="B119">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C119">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D119">
         <v>-1</v>
       </c>
       <c r="E119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ゴーストアーマー</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C120">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D120">
         <v>-1</v>
       </c>
       <c r="E120" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B120,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>2010</v>
+        <v>1040</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C121">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D121">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C122">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D122">
         <v>-1</v>
       </c>
       <c r="E122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C123">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D123">
         <v>-1</v>
       </c>
       <c r="E123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>2010</v>
+        <v>1050</v>
       </c>
       <c r="B124">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C124">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D124">
         <v>-1</v>
       </c>
       <c r="E124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -6453,7 +6521,7 @@
         <v>2010</v>
       </c>
       <c r="B125">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -6463,7 +6531,7 @@
       </c>
       <c r="E125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -6471,7 +6539,7 @@
         <v>2010</v>
       </c>
       <c r="B126">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -6481,97 +6549,97 @@
       </c>
       <c r="E126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D128">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B129">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B130">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B131">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6579,7 +6647,7 @@
         <v>2020</v>
       </c>
       <c r="B132">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C132">
         <v>7</v>
@@ -6589,7 +6657,7 @@
       </c>
       <c r="E132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -6597,7 +6665,7 @@
         <v>2020</v>
       </c>
       <c r="B133">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -6607,7 +6675,7 @@
       </c>
       <c r="E133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6615,17 +6683,17 @@
         <v>2020</v>
       </c>
       <c r="B134">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C134">
         <v>7</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6633,16 +6701,106 @@
         <v>2020</v>
       </c>
       <c r="B135">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C135">
         <v>7</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>2020</v>
+      </c>
+      <c r="B136">
+        <v>8</v>
+      </c>
+      <c r="C136">
+        <v>7</v>
+      </c>
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>2020</v>
+      </c>
+      <c r="B137">
+        <v>9</v>
+      </c>
+      <c r="C137">
+        <v>7</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>2020</v>
+      </c>
+      <c r="B138">
+        <v>12</v>
+      </c>
+      <c r="C138">
+        <v>7</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>2020</v>
+      </c>
+      <c r="B139">
+        <v>13</v>
+      </c>
+      <c r="C139">
+        <v>7</v>
+      </c>
+      <c r="D139">
+        <v>2</v>
+      </c>
+      <c r="E139" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>2020</v>
+      </c>
+      <c r="B140">
+        <v>14</v>
+      </c>
+      <c r="C140">
+        <v>7</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+      <c r="E140" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
         <v>クリーパー</v>
       </c>
     </row>
@@ -6655,7 +6813,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="34.1818181818182" customWidth="1"/>
@@ -6955,43 +7113,43 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="39" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="39" spans="1:7">
+      <c r="A19">
+        <v>60</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>61</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>88</v>
@@ -7008,7 +7166,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>90</v>
@@ -7025,7 +7183,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>92</v>
@@ -7040,52 +7198,52 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" ht="26" spans="1:7">
+    <row r="23" spans="1:7">
       <c r="A23">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="26" spans="1:7">
+      <c r="A24">
+        <v>70</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>71</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -7093,16 +7251,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -7110,166 +7268,183 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" ht="25" spans="1:7">
+    <row r="28" spans="1:7">
       <c r="A28">
-        <v>1010</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>101</v>
+      <c r="G28" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="29" ht="25" spans="1:7">
       <c r="A29">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="30" ht="25" spans="1:7">
       <c r="A30">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31" ht="25" spans="1:7">
       <c r="A31">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" ht="25" spans="1:7">
       <c r="A32">
+        <v>1040</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" ht="25" spans="1:7">
+      <c r="A33">
         <v>1050</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="C33" s="4" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="33" ht="37.5" spans="1:7">
-      <c r="A33">
-        <v>2010</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="34" ht="37.5" spans="1:7">
       <c r="A34">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="35" ht="37.5" spans="1:7">
       <c r="A35">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G35" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" ht="37.5" spans="1:7">
+      <c r="A36">
+        <v>2030</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="36" spans="3:4">
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="3:3">
+      <c r="F36" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
       <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="3:3">
       <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7290,19 +7465,19 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7310,31 +7485,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I2">
         <v>-1</v>
       </c>
       <c r="J2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K2">
         <v>-1</v>
       </c>
       <c r="L2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -7342,34 +7517,34 @@
         <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D3">
         <v>1010</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M3">
         <v>10</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -7377,34 +7552,34 @@
         <v>210</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D4">
         <v>1020</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K4">
         <v>11</v>
       </c>
       <c r="L4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M4">
         <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" ht="39" spans="1:15">
@@ -7412,34 +7587,34 @@
         <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D5">
         <v>1030</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K5">
         <v>20</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M5">
         <v>30</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -7447,34 +7622,34 @@
         <v>2010</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D6">
         <v>2010</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I6">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K6">
         <v>30</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M6">
         <v>40</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -7482,34 +7657,34 @@
         <v>3010</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D7">
         <v>2011</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I7">
         <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K7">
         <v>40</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M7">
         <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" ht="39" spans="4:15">
@@ -7517,28 +7692,28 @@
         <v>2020</v>
       </c>
       <c r="E8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I8">
         <v>40</v>
       </c>
       <c r="J8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K8">
         <v>50</v>
       </c>
       <c r="L8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M8">
         <v>60</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="4:15">
@@ -7546,28 +7721,28 @@
         <v>2021</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K9">
         <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M9">
         <v>70</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="4:15">
@@ -7575,28 +7750,28 @@
         <v>2030</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I10">
         <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K10">
         <v>70</v>
       </c>
       <c r="L10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M10">
         <v>80</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="4:12">
@@ -7604,19 +7779,19 @@
         <v>3010</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I11">
         <v>70</v>
       </c>
       <c r="J11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K11">
         <v>80</v>
       </c>
       <c r="L11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="4:12">
@@ -7624,19 +7799,19 @@
         <v>3020</v>
       </c>
       <c r="E12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I12">
         <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K12">
         <v>90</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="4:12">
@@ -7644,19 +7819,19 @@
         <v>3030</v>
       </c>
       <c r="E13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K13">
         <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="4:12">
@@ -7664,13 +7839,13 @@
         <v>4010</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="4:5">
@@ -7678,7 +7853,7 @@
         <v>4011</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="4:5">
@@ -7686,7 +7861,7 @@
         <v>4020</v>
       </c>
       <c r="E16" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -7694,7 +7869,7 @@
         <v>5010</v>
       </c>
       <c r="E17" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -7702,7 +7877,7 @@
         <v>5020</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -7710,7 +7885,7 @@
         <v>6010</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -7718,7 +7893,7 @@
         <v>6011</v>
       </c>
       <c r="E20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -7726,7 +7901,7 @@
         <v>6020</v>
       </c>
       <c r="E21" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="4:5">
@@ -7734,7 +7909,7 @@
         <v>6030</v>
       </c>
       <c r="E22" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="4:5">
@@ -7742,7 +7917,7 @@
         <v>7010</v>
       </c>
       <c r="E23" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -7750,7 +7925,7 @@
         <v>7020</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -7758,7 +7933,7 @@
         <v>7021</v>
       </c>
       <c r="E25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -7766,7 +7941,7 @@
         <v>8010</v>
       </c>
       <c r="E26" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -7774,7 +7949,7 @@
         <v>9010</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="5:5">

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -642,10 +642,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -668,29 +668,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -705,6 +682,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -714,7 +714,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -736,16 +751,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -759,9 +766,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -769,21 +783,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -797,16 +796,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -821,13 +821,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -839,13 +881,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -857,37 +899,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -905,7 +935,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -917,67 +983,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -989,19 +1001,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1030,6 +1030,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1039,13 +1063,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1067,24 +1095,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1097,21 +1112,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1120,145 +1120,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>30</v>
@@ -3095,7 +3095,7 @@
         <v>2040</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -3139,10 +3139,10 @@
         <v>30</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -3157,7 +3157,7 @@
         <v>2040</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -3201,10 +3201,10 @@
         <v>30</v>
       </c>
       <c r="K20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -3219,7 +3219,7 @@
         <v>2040</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="R20" t="s">
         <v>26</v>
@@ -3263,10 +3263,10 @@
         <v>30</v>
       </c>
       <c r="K21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -3281,7 +3281,7 @@
         <v>2040</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R21" t="s">
         <v>26</v>
@@ -4282,7 +4282,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.45454545454546" customWidth="1"/>
@@ -5459,17 +5459,17 @@
         <v>61</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D66">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E66" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B66,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -5477,17 +5477,17 @@
         <v>61</v>
       </c>
       <c r="B67">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D67">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B67,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -5495,679 +5495,679 @@
         <v>61</v>
       </c>
       <c r="B68">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D68">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E68" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B68,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B69">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D69">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B69,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B70">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D70">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E70" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B70,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B71">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D71">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E71" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B71,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C72">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D72">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B72,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B73">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B73,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B74">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C74">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B74,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C75">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D75">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B75,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C76">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D76">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B76,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B77">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D77">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B77,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B78">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D78">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B78,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B79">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D79">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E79" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B79,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B80">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C80">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D80">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E80" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B80,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B81">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C81">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D81">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B81,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C82">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D82">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E82" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B82,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D83">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E83" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B83,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B84">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D84">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E84" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B84,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B85">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D85">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B85,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B86">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C86">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D86">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E86" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B86,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B87">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D87">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B87,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B88">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D88">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B88,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B89">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D89">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B89,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B90">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D90">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B90,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B91">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C91">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D91">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B91,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B92">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C92">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D92">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E92" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B92,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B93">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C93">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D93">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E93" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B93,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B94">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C94">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D94">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E94" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B94,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>スコーピオン</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C95">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D95">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E95" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B95,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B96">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D96">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B96,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B97">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D97">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E97" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B97,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B98">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D98">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E98" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B98,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B99">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D99">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E99" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B99,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ネレイドジェム</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B100">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D100">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B100,[1]TextData!A:A))</f>
-        <v>スクイッド</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B101">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D101">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E101" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B101,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102">
-        <v>1010</v>
+        <v>64</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D102">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E102" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B102,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>クロウ</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103">
-        <v>1010</v>
+        <v>64</v>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C103">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D103">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B103,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104">
-        <v>1010</v>
+        <v>64</v>
       </c>
       <c r="B104">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C104">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D104">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B104,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105">
-        <v>1010</v>
+        <v>64</v>
       </c>
       <c r="B105">
         <v>10</v>
       </c>
       <c r="C105">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D105">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E105" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B105,[1]TextData!A:A))</f>
@@ -6176,265 +6176,265 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106">
-        <v>1020</v>
+        <v>64</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C106">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D106">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E106" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B106,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107">
-        <v>1020</v>
+        <v>64</v>
       </c>
       <c r="B107">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C107">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D107">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B107,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108">
-        <v>1020</v>
+        <v>64</v>
       </c>
       <c r="B108">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C108">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D108">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B108,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109">
-        <v>1020</v>
+        <v>64</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C109">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D109">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E109" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B109,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110">
-        <v>1020</v>
+        <v>70</v>
       </c>
       <c r="B110">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D110">
         <v>-1</v>
       </c>
       <c r="E110" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B110,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C111">
         <v>10</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B111,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C112">
         <v>10</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B112,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="B113">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C113">
         <v>10</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E113" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B113,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="B114">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C114">
         <v>10</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E114" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B114,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="B115">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C115">
         <v>10</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E115" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B115,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116">
-        <v>1030</v>
+        <v>70</v>
       </c>
       <c r="B116">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C116">
         <v>10</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E116" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B116,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117">
-        <v>1040</v>
+        <v>71</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D117">
         <v>-1</v>
       </c>
       <c r="E117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B117,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118">
-        <v>1040</v>
+        <v>71</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D118">
         <v>-1</v>
       </c>
       <c r="E118" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B118,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119">
-        <v>1040</v>
+        <v>71</v>
       </c>
       <c r="B119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D119">
         <v>-1</v>
       </c>
       <c r="E119" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B119,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120">
-        <v>1040</v>
+        <v>71</v>
       </c>
       <c r="B120">
         <v>8</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D120">
         <v>-1</v>
@@ -6446,16 +6446,16 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121">
-        <v>1040</v>
+        <v>71</v>
       </c>
       <c r="B121">
         <v>13</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D121">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B121,[1]TextData!A:A))</f>
@@ -6464,64 +6464,64 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122">
-        <v>1050</v>
+        <v>71</v>
       </c>
       <c r="B122">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D122">
         <v>-1</v>
       </c>
       <c r="E122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B122,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123">
-        <v>1050</v>
+        <v>71</v>
       </c>
       <c r="B123">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D123">
         <v>-1</v>
       </c>
       <c r="E123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B123,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124">
-        <v>1050</v>
+        <v>72</v>
       </c>
       <c r="B124">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C124">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D124">
         <v>-1</v>
       </c>
       <c r="E124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B124,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125">
-        <v>2010</v>
+        <v>72</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C125">
         <v>10</v>
@@ -6531,15 +6531,15 @@
       </c>
       <c r="E125" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B125,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126">
-        <v>2010</v>
+        <v>72</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C126">
         <v>10</v>
@@ -6549,15 +6549,15 @@
       </c>
       <c r="E126" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B126,[1]TextData!A:A))</f>
-        <v>ビー</v>
+        <v>ネームレス</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127">
-        <v>2010</v>
+        <v>72</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C127">
         <v>10</v>
@@ -6567,15 +6567,15 @@
       </c>
       <c r="E127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B127,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128">
-        <v>2010</v>
+        <v>72</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C128">
         <v>10</v>
@@ -6585,15 +6585,15 @@
       </c>
       <c r="E128" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B128,[1]TextData!A:A))</f>
-        <v>クロウ</v>
+        <v>クリーパー</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129">
-        <v>2010</v>
+        <v>72</v>
       </c>
       <c r="B129">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C129">
         <v>10</v>
@@ -6603,15 +6603,15 @@
       </c>
       <c r="E129" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B129,[1]TextData!A:A))</f>
-        <v>サーチャー</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130">
-        <v>2010</v>
+        <v>73</v>
       </c>
       <c r="B130">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C130">
         <v>10</v>
@@ -6621,15 +6621,15 @@
       </c>
       <c r="E130" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B130,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>カースド</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131">
-        <v>2010</v>
+        <v>73</v>
       </c>
       <c r="B131">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C131">
         <v>10</v>
@@ -6639,168 +6639,798 @@
       </c>
       <c r="E131" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B131,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132">
-        <v>2020</v>
+        <v>73</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E132" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B132,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>サーチャー</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133">
-        <v>2020</v>
+        <v>73</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E133" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B133,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134">
-        <v>2020</v>
+        <v>73</v>
       </c>
       <c r="B134">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E134" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B134,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>インプ</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135">
-        <v>2020</v>
+        <v>73</v>
       </c>
       <c r="B135">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E135" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B135,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>スクイッド</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136">
-        <v>2020</v>
+        <v>73</v>
       </c>
       <c r="B136">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E136" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B136,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>ソード</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="B137">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E137" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B137,[1]TextData!A:A))</f>
-        <v>ドライアド</v>
+        <v>ビー</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="B138">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E138" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B138,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ウルフ</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="B139">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E139" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B139,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>ドライアド</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140">
-        <v>2020</v>
+        <v>1010</v>
       </c>
       <c r="B140">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E140" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(B140,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>1020</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>15</v>
+      </c>
+      <c r="D141">
+        <v>-1</v>
+      </c>
+      <c r="E141" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B141,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142">
+        <v>1020</v>
+      </c>
+      <c r="B142">
+        <v>3</v>
+      </c>
+      <c r="C142">
+        <v>15</v>
+      </c>
+      <c r="D142">
+        <v>-1</v>
+      </c>
+      <c r="E142" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B142,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143">
+        <v>1020</v>
+      </c>
+      <c r="B143">
+        <v>4</v>
+      </c>
+      <c r="C143">
+        <v>15</v>
+      </c>
+      <c r="D143">
+        <v>-1</v>
+      </c>
+      <c r="E143" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B143,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144">
+        <v>1020</v>
+      </c>
+      <c r="B144">
+        <v>5</v>
+      </c>
+      <c r="C144">
+        <v>15</v>
+      </c>
+      <c r="D144">
+        <v>-1</v>
+      </c>
+      <c r="E144" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B144,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145">
+        <v>1020</v>
+      </c>
+      <c r="B145">
+        <v>7</v>
+      </c>
+      <c r="C145">
+        <v>15</v>
+      </c>
+      <c r="D145">
+        <v>-1</v>
+      </c>
+      <c r="E145" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B145,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146">
+        <v>1030</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146">
+        <v>10</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B146,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147">
+        <v>1030</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147">
+        <v>10</v>
+      </c>
+      <c r="D147">
+        <v>2</v>
+      </c>
+      <c r="E147" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B147,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148">
+        <v>1030</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>10</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+      <c r="E148" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B148,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149">
+        <v>1030</v>
+      </c>
+      <c r="B149">
+        <v>9</v>
+      </c>
+      <c r="C149">
+        <v>10</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B149,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150">
+        <v>1030</v>
+      </c>
+      <c r="B150">
+        <v>12</v>
+      </c>
+      <c r="C150">
+        <v>10</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B150,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151">
+        <v>1030</v>
+      </c>
+      <c r="B151">
+        <v>14</v>
+      </c>
+      <c r="C151">
+        <v>10</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+      <c r="E151" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B151,[1]TextData!A:A))</f>
+        <v>クリーパー</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152">
+        <v>1040</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>7</v>
+      </c>
+      <c r="D152">
+        <v>-1</v>
+      </c>
+      <c r="E152" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B152,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153">
+        <v>1040</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>7</v>
+      </c>
+      <c r="D153">
+        <v>-1</v>
+      </c>
+      <c r="E153" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B153,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154">
+        <v>1040</v>
+      </c>
+      <c r="B154">
+        <v>6</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+      <c r="D154">
+        <v>-1</v>
+      </c>
+      <c r="E154" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B154,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155">
+        <v>1040</v>
+      </c>
+      <c r="B155">
+        <v>8</v>
+      </c>
+      <c r="C155">
+        <v>7</v>
+      </c>
+      <c r="D155">
+        <v>-1</v>
+      </c>
+      <c r="E155" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B155,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156">
+        <v>1040</v>
+      </c>
+      <c r="B156">
+        <v>13</v>
+      </c>
+      <c r="C156">
+        <v>7</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+      <c r="E156" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B156,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157">
+        <v>1050</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+      <c r="C157">
+        <v>15</v>
+      </c>
+      <c r="D157">
+        <v>-1</v>
+      </c>
+      <c r="E157" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B157,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158">
+        <v>1050</v>
+      </c>
+      <c r="B158">
+        <v>13</v>
+      </c>
+      <c r="C158">
+        <v>15</v>
+      </c>
+      <c r="D158">
+        <v>-1</v>
+      </c>
+      <c r="E158" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B158,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159">
+        <v>1050</v>
+      </c>
+      <c r="B159">
+        <v>15</v>
+      </c>
+      <c r="C159">
+        <v>15</v>
+      </c>
+      <c r="D159">
+        <v>-1</v>
+      </c>
+      <c r="E159" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B159,[1]TextData!A:A))</f>
+        <v>ソード</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160">
+        <v>2010</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>10</v>
+      </c>
+      <c r="D160">
+        <v>-1</v>
+      </c>
+      <c r="E160" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B160,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161">
+        <v>2010</v>
+      </c>
+      <c r="B161">
+        <v>3</v>
+      </c>
+      <c r="C161">
+        <v>10</v>
+      </c>
+      <c r="D161">
+        <v>-1</v>
+      </c>
+      <c r="E161" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B161,[1]TextData!A:A))</f>
+        <v>ビー</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162">
+        <v>2010</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>10</v>
+      </c>
+      <c r="D162">
+        <v>-1</v>
+      </c>
+      <c r="E162" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B162,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163">
+        <v>2010</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+      <c r="C163">
+        <v>10</v>
+      </c>
+      <c r="D163">
+        <v>-1</v>
+      </c>
+      <c r="E163" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B163,[1]TextData!A:A))</f>
+        <v>クロウ</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164">
+        <v>2010</v>
+      </c>
+      <c r="B164">
+        <v>7</v>
+      </c>
+      <c r="C164">
+        <v>10</v>
+      </c>
+      <c r="D164">
+        <v>-1</v>
+      </c>
+      <c r="E164" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B164,[1]TextData!A:A))</f>
+        <v>サーチャー</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165">
+        <v>2010</v>
+      </c>
+      <c r="B165">
+        <v>9</v>
+      </c>
+      <c r="C165">
+        <v>10</v>
+      </c>
+      <c r="D165">
+        <v>-1</v>
+      </c>
+      <c r="E165" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B165,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166">
+        <v>2010</v>
+      </c>
+      <c r="B166">
+        <v>10</v>
+      </c>
+      <c r="C166">
+        <v>10</v>
+      </c>
+      <c r="D166">
+        <v>-1</v>
+      </c>
+      <c r="E166" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B166,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167">
+        <v>2020</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167">
+        <v>7</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B167,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168">
+        <v>2020</v>
+      </c>
+      <c r="B168">
+        <v>2</v>
+      </c>
+      <c r="C168">
+        <v>7</v>
+      </c>
+      <c r="D168">
+        <v>2</v>
+      </c>
+      <c r="E168" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B168,[1]TextData!A:A))</f>
+        <v>カースド</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169">
+        <v>2020</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169">
+        <v>7</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B169,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170">
+        <v>2020</v>
+      </c>
+      <c r="B170">
+        <v>6</v>
+      </c>
+      <c r="C170">
+        <v>7</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B170,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171">
+        <v>2020</v>
+      </c>
+      <c r="B171">
+        <v>8</v>
+      </c>
+      <c r="C171">
+        <v>7</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B171,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172">
+        <v>2020</v>
+      </c>
+      <c r="B172">
+        <v>9</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+      <c r="E172" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B172,[1]TextData!A:A))</f>
+        <v>ドライアド</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173">
+        <v>2020</v>
+      </c>
+      <c r="B173">
+        <v>12</v>
+      </c>
+      <c r="C173">
+        <v>7</v>
+      </c>
+      <c r="D173">
+        <v>2</v>
+      </c>
+      <c r="E173" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B173,[1]TextData!A:A))</f>
+        <v>ネームレス</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174">
+        <v>2020</v>
+      </c>
+      <c r="B174">
+        <v>13</v>
+      </c>
+      <c r="C174">
+        <v>7</v>
+      </c>
+      <c r="D174">
+        <v>2</v>
+      </c>
+      <c r="E174" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B174,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175">
+        <v>2020</v>
+      </c>
+      <c r="B175">
+        <v>14</v>
+      </c>
+      <c r="C175">
+        <v>7</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="E175" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(B175,[1]TextData!A:A))</f>
         <v>クリーパー</v>
       </c>
     </row>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -669,13 +669,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -689,9 +682,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -705,14 +705,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -720,16 +712,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -752,36 +759,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -789,7 +766,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -804,9 +781,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -821,7 +821,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,37 +965,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -875,19 +977,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -899,109 +1001,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1030,50 +1030,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1107,8 +1068,47 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1120,7 +1120,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1129,136 +1129,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3372,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>30</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>30</v>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <v>30</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <v>30</v>
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>30</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>30</v>
@@ -3927,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J32">
         <v>30</v>

--- a/Assets/Data/Stages.xlsx
+++ b/Assets/Data/Stages.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="802" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Stages" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="197">
   <si>
     <t>Id</t>
   </si>
@@ -574,28 +574,31 @@
     <t>離脱ポイントへ向かう。攻撃してこない。</t>
   </si>
   <si>
+    <t>ダンジョン移動前に向き変更</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
     <t>アーティファクト取得</t>
   </si>
   <si>
-    <t>Shop</t>
+    <t>Gacha</t>
   </si>
   <si>
     <t>アイテム取得</t>
   </si>
   <si>
-    <t>Gacha</t>
+    <t>Group</t>
   </si>
   <si>
     <t>魔法入手</t>
   </si>
   <si>
-    <t>Group</t>
+    <t>Battler</t>
   </si>
   <si>
     <t>仲間を増やす</t>
-  </si>
-  <si>
-    <t>Battler</t>
   </si>
   <si>
     <t>仲間を外す</t>
@@ -669,14 +672,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -684,6 +680,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -697,8 +708,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -706,14 +732,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -727,30 +761,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -759,30 +769,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -790,9 +777,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -811,6 +798,22 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -821,7 +824,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -851,7 +854,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,13 +872,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,13 +890,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -899,25 +914,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -935,13 +938,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -953,13 +974,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -971,37 +992,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1030,15 +1033,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1050,17 +1044,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1083,17 +1066,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1112,6 +1089,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1120,7 +1123,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1129,13 +1132,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -1144,121 +1147,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8406,7 +8409,7 @@
     </row>
     <row r="11" spans="4:12">
       <c r="D11">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="E11" t="s">
         <v>175</v>
@@ -8426,7 +8429,7 @@
     </row>
     <row r="12" spans="4:12">
       <c r="D12">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="E12" t="s">
         <v>177</v>
@@ -8446,7 +8449,7 @@
     </row>
     <row r="13" spans="4:12">
       <c r="D13">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="E13" t="s">
         <v>179</v>
@@ -8466,7 +8469,7 @@
     </row>
     <row r="14" spans="4:12">
       <c r="D14">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="E14" t="s">
         <v>181</v>
@@ -8480,7 +8483,7 @@
     </row>
     <row r="15" spans="4:5">
       <c r="D15">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="E15" t="s">
         <v>183</v>
@@ -8488,7 +8491,7 @@
     </row>
     <row r="16" spans="4:5">
       <c r="D16">
-        <v>4020</v>
+        <v>4011</v>
       </c>
       <c r="E16" t="s">
         <v>184</v>
@@ -8496,7 +8499,7 @@
     </row>
     <row r="17" spans="4:5">
       <c r="D17">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="E17" t="s">
         <v>185</v>
@@ -8504,7 +8507,7 @@
     </row>
     <row r="18" spans="4:5">
       <c r="D18">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="E18" t="s">
         <v>186</v>
@@ -8512,7 +8515,7 @@
     </row>
     <row r="19" spans="4:5">
       <c r="D19">
-        <v>6010</v>
+        <v>5020</v>
       </c>
       <c r="E19" t="s">
         <v>187</v>
@@ -8520,7 +8523,7 @@
     </row>
     <row r="20" spans="4:5">
       <c r="D20">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="E20" t="s">
         <v>188</v>
@@ -8528,7 +8531,7 @@
     </row>
     <row r="21" spans="4:5">
       <c r="D21">
-        <v>6020</v>
+        <v>6011</v>
       </c>
       <c r="E21" t="s">
         <v>189</v>
@@ -8536,7 +8539,7 @@
     </row>
     <row r="22" spans="4:5">
       <c r="D22">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="E22" t="s">
         <v>190</v>
@@ -8544,7 +8547,7 @@
     </row>
     <row r="23" spans="4:5">
       <c r="D23">
-        <v>7010</v>
+        <v>6030</v>
       </c>
       <c r="E23" t="s">
         <v>191</v>
@@ -8552,7 +8555,7 @@
     </row>
     <row r="24" spans="4:5">
       <c r="D24">
-        <v>7020</v>
+        <v>7010</v>
       </c>
       <c r="E24" t="s">
         <v>192</v>
@@ -8560,7 +8563,7 @@
     </row>
     <row r="25" spans="4:5">
       <c r="D25">
-        <v>7021</v>
+        <v>7020</v>
       </c>
       <c r="E25" t="s">
         <v>193</v>
@@ -8568,7 +8571,7 @@
     </row>
     <row r="26" spans="4:5">
       <c r="D26">
-        <v>8010</v>
+        <v>7021</v>
       </c>
       <c r="E26" t="s">
         <v>194</v>
@@ -8576,14 +8579,19 @@
     </row>
     <row r="27" spans="4:5">
       <c r="D27">
-        <v>9010</v>
+        <v>8010</v>
       </c>
       <c r="E27" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="5:5">
-      <c r="E28" s="1"/>
+    <row r="28" spans="4:5">
+      <c r="D28">
+        <v>9010</v>
+      </c>
+      <c r="E28" t="s">
+        <v>196</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
